--- a/docs/verify/sample_materials.xlsx
+++ b/docs/verify/sample_materials.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="89">
   <si>
     <t>船 名</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>作業者D</t>
+  </si>
+  <si>
+    <t>合計</t>
   </si>
   <si>
     <t>材　　　　料　　　　持　　　　出　　　　表</t>
@@ -293,13 +296,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="165" formatCode="[h]:mm"/>
     <numFmt numFmtId="166" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;-#,##0"/>
-    <numFmt numFmtId="167" formatCode="m/d;@"/>
+    <numFmt numFmtId="167" formatCode="&quot;¥&quot;#,##0_);[Red](&quot;¥&quot;#,##0)"/>
+    <numFmt numFmtId="168" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -338,6 +342,13 @@
       <name val="游ゴシック"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+    </font>
+    <font>
       <b/>
       <charset val="128"/>
       <color indexed="8"/>
@@ -353,7 +364,7 @@
       <name val="游ゴシック"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,6 +373,12 @@
     </fill>
     <fill>
       <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -428,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -474,11 +491,27 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -494,7 +527,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -504,13 +537,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -831,8 +864,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>20</v>
+      <c r="A1" s="30" t="s">
+        <v>21</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -890,13 +923,13 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -906,7 +939,7 @@
       <c r="K2" s="9"/>
       <c r="L2" s="10"/>
       <c r="M2" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
@@ -916,50 +949,50 @@
       <c r="S2" s="9"/>
       <c r="T2" s="10"/>
       <c r="U2" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V2" s="9"/>
       <c r="W2" s="10"/>
       <c r="X2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="10"/>
       <c r="AB2" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC2" s="9"/>
       <c r="AD2" s="9"/>
       <c r="AE2" s="10"/>
       <c r="AF2" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG2" s="9"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="10"/>
       <c r="AJ2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK2" s="9"/>
       <c r="AL2" s="9"/>
       <c r="AM2" s="9"/>
       <c r="AN2" s="10"/>
       <c r="AO2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP2" s="9"/>
       <c r="AQ2" s="9"/>
       <c r="AR2" s="10"/>
       <c r="AS2" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AT2" s="9"/>
       <c r="AU2" s="9"/>
       <c r="AV2" s="9"/>
       <c r="AW2" s="10"/>
       <c r="AX2" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AY2" s="9"/>
       <c r="AZ2" s="9"/>
@@ -967,7 +1000,7 @@
       <c r="BB2" s="10"/>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21"/>
+      <c r="A3" s="27"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
@@ -994,44 +1027,44 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
       <c r="AA3" s="10"/>
-      <c r="AB3" s="18"/>
+      <c r="AB3" s="24"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
-      <c r="AE3" s="19"/>
-      <c r="AF3" s="20"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="26"/>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
       <c r="AI3" s="5"/>
-      <c r="AJ3" s="20">
+      <c r="AJ3" s="26">
         <f>SUM(AF3*AB3)</f>
       </c>
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
       <c r="AM3" s="4"/>
       <c r="AN3" s="5"/>
-      <c r="AO3" s="20"/>
+      <c r="AO3" s="26"/>
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="5"/>
-      <c r="AS3" s="20">
+      <c r="AS3" s="26">
         <f>SUM(AO3*AB3)</f>
       </c>
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
       <c r="AV3" s="4"/>
       <c r="AW3" s="5"/>
-      <c r="AX3" s="20"/>
+      <c r="AX3" s="26"/>
       <c r="AY3" s="4"/>
       <c r="AZ3" s="4"/>
       <c r="BA3" s="4"/>
       <c r="BB3" s="5"/>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="25"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -1054,44 +1087,44 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
       <c r="AA4" s="10"/>
-      <c r="AB4" s="18"/>
+      <c r="AB4" s="24"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
-      <c r="AE4" s="19"/>
-      <c r="AF4" s="20"/>
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="26"/>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
       <c r="AI4" s="5"/>
-      <c r="AJ4" s="20">
+      <c r="AJ4" s="26">
         <f>SUM(AF4*AB4)</f>
       </c>
       <c r="AK4" s="4"/>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
       <c r="AN4" s="5"/>
-      <c r="AO4" s="20"/>
+      <c r="AO4" s="26"/>
       <c r="AP4" s="4"/>
       <c r="AQ4" s="4"/>
       <c r="AR4" s="5"/>
-      <c r="AS4" s="20">
+      <c r="AS4" s="26">
         <f>SUM(AO4*AB4)</f>
       </c>
       <c r="AT4" s="4"/>
       <c r="AU4" s="4"/>
       <c r="AV4" s="4"/>
       <c r="AW4" s="5"/>
-      <c r="AX4" s="20"/>
+      <c r="AX4" s="26"/>
       <c r="AY4" s="4"/>
       <c r="AZ4" s="4"/>
       <c r="BA4" s="4"/>
       <c r="BB4" s="5"/>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="10"/>
-      <c r="E5" s="25"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -1114,40 +1147,40 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
       <c r="AA5" s="10"/>
-      <c r="AB5" s="18"/>
+      <c r="AB5" s="24"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
-      <c r="AE5" s="19"/>
-      <c r="AF5" s="20"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="26"/>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
       <c r="AI5" s="5"/>
-      <c r="AJ5" s="20">
+      <c r="AJ5" s="26">
         <f>SUM(AF5*AB5)</f>
       </c>
       <c r="AK5" s="4"/>
       <c r="AL5" s="4"/>
       <c r="AM5" s="4"/>
       <c r="AN5" s="5"/>
-      <c r="AO5" s="20"/>
+      <c r="AO5" s="26"/>
       <c r="AP5" s="4"/>
       <c r="AQ5" s="4"/>
       <c r="AR5" s="5"/>
-      <c r="AS5" s="20">
+      <c r="AS5" s="26">
         <f>SUM(AO5*AB5)</f>
       </c>
       <c r="AT5" s="4"/>
       <c r="AU5" s="4"/>
       <c r="AV5" s="4"/>
       <c r="AW5" s="5"/>
-      <c r="AX5" s="20"/>
+      <c r="AX5" s="26"/>
       <c r="AY5" s="4"/>
       <c r="AZ5" s="4"/>
       <c r="BA5" s="4"/>
       <c r="BB5" s="5"/>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="10"/>
@@ -1174,44 +1207,44 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="10"/>
-      <c r="AB6" s="18"/>
+      <c r="AB6" s="24"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="20"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="26"/>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
       <c r="AI6" s="5"/>
-      <c r="AJ6" s="20">
+      <c r="AJ6" s="26">
         <f>SUM(AF6*AB6)</f>
       </c>
       <c r="AK6" s="4"/>
       <c r="AL6" s="4"/>
       <c r="AM6" s="4"/>
       <c r="AN6" s="5"/>
-      <c r="AO6" s="20"/>
+      <c r="AO6" s="26"/>
       <c r="AP6" s="4"/>
       <c r="AQ6" s="4"/>
       <c r="AR6" s="5"/>
-      <c r="AS6" s="20">
+      <c r="AS6" s="26">
         <f>SUM(AO6*AB6)</f>
       </c>
       <c r="AT6" s="4"/>
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
       <c r="AW6" s="5"/>
-      <c r="AX6" s="20"/>
+      <c r="AX6" s="26"/>
       <c r="AY6" s="4"/>
       <c r="AZ6" s="4"/>
       <c r="BA6" s="4"/>
       <c r="BB6" s="5"/>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="26"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -1234,40 +1267,40 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
       <c r="AA7" s="10"/>
-      <c r="AB7" s="18"/>
+      <c r="AB7" s="24"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="20"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="26"/>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="20">
+      <c r="AJ7" s="26">
         <f>SUM(AF7*AB7)</f>
       </c>
       <c r="AK7" s="4"/>
       <c r="AL7" s="4"/>
       <c r="AM7" s="4"/>
       <c r="AN7" s="5"/>
-      <c r="AO7" s="20"/>
+      <c r="AO7" s="26"/>
       <c r="AP7" s="4"/>
       <c r="AQ7" s="4"/>
       <c r="AR7" s="5"/>
-      <c r="AS7" s="20">
+      <c r="AS7" s="26">
         <f>SUM(AO7*AB7)</f>
       </c>
       <c r="AT7" s="4"/>
       <c r="AU7" s="4"/>
       <c r="AV7" s="4"/>
       <c r="AW7" s="5"/>
-      <c r="AX7" s="20"/>
+      <c r="AX7" s="26"/>
       <c r="AY7" s="4"/>
       <c r="AZ7" s="4"/>
       <c r="BA7" s="4"/>
       <c r="BB7" s="5"/>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="10"/>
@@ -1279,7 +1312,7 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="25"/>
+      <c r="M8" s="31"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
@@ -1294,44 +1327,44 @@
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="10"/>
-      <c r="AB8" s="18"/>
+      <c r="AB8" s="24"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="20"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="26"/>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
       <c r="AI8" s="5"/>
-      <c r="AJ8" s="20">
+      <c r="AJ8" s="26">
         <f>SUM(AF8*AB8)</f>
       </c>
       <c r="AK8" s="4"/>
       <c r="AL8" s="4"/>
       <c r="AM8" s="4"/>
       <c r="AN8" s="5"/>
-      <c r="AO8" s="20"/>
+      <c r="AO8" s="26"/>
       <c r="AP8" s="4"/>
       <c r="AQ8" s="4"/>
       <c r="AR8" s="5"/>
-      <c r="AS8" s="20">
+      <c r="AS8" s="26">
         <f>SUM(AO8*AB8)</f>
       </c>
       <c r="AT8" s="4"/>
       <c r="AU8" s="4"/>
       <c r="AV8" s="4"/>
       <c r="AW8" s="5"/>
-      <c r="AX8" s="20"/>
+      <c r="AX8" s="26"/>
       <c r="AY8" s="4"/>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
       <c r="BB8" s="5"/>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="26"/>
+      <c r="E9" s="32"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
@@ -1354,40 +1387,40 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
       <c r="AA9" s="10"/>
-      <c r="AB9" s="18"/>
+      <c r="AB9" s="24"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="20"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="26"/>
       <c r="AG9" s="4"/>
       <c r="AH9" s="4"/>
       <c r="AI9" s="5"/>
-      <c r="AJ9" s="20">
+      <c r="AJ9" s="26">
         <f>SUM(AF9*AB9)</f>
       </c>
       <c r="AK9" s="4"/>
       <c r="AL9" s="4"/>
       <c r="AM9" s="4"/>
       <c r="AN9" s="5"/>
-      <c r="AO9" s="20"/>
+      <c r="AO9" s="26"/>
       <c r="AP9" s="4"/>
       <c r="AQ9" s="4"/>
       <c r="AR9" s="5"/>
-      <c r="AS9" s="20">
+      <c r="AS9" s="26">
         <f>SUM(AO9*AB9)</f>
       </c>
       <c r="AT9" s="4"/>
       <c r="AU9" s="4"/>
       <c r="AV9" s="4"/>
       <c r="AW9" s="5"/>
-      <c r="AX9" s="20"/>
+      <c r="AX9" s="26"/>
       <c r="AY9" s="4"/>
       <c r="AZ9" s="4"/>
       <c r="BA9" s="4"/>
       <c r="BB9" s="5"/>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -1414,40 +1447,40 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="10"/>
-      <c r="AB10" s="18"/>
+      <c r="AB10" s="24"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="20"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="26"/>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
       <c r="AI10" s="5"/>
-      <c r="AJ10" s="20">
+      <c r="AJ10" s="26">
         <f>SUM(AF10*AB10)</f>
       </c>
       <c r="AK10" s="4"/>
       <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
       <c r="AN10" s="5"/>
-      <c r="AO10" s="20"/>
+      <c r="AO10" s="26"/>
       <c r="AP10" s="4"/>
       <c r="AQ10" s="4"/>
       <c r="AR10" s="5"/>
-      <c r="AS10" s="20">
+      <c r="AS10" s="26">
         <f>SUM(AO10*AB10)</f>
       </c>
       <c r="AT10" s="4"/>
       <c r="AU10" s="4"/>
       <c r="AV10" s="4"/>
       <c r="AW10" s="5"/>
-      <c r="AX10" s="20"/>
+      <c r="AX10" s="26"/>
       <c r="AY10" s="4"/>
       <c r="AZ10" s="4"/>
       <c r="BA10" s="4"/>
       <c r="BB10" s="5"/>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="10"/>
@@ -1474,40 +1507,40 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
       <c r="AA11" s="10"/>
-      <c r="AB11" s="18"/>
+      <c r="AB11" s="24"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="20"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="26"/>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="5"/>
-      <c r="AJ11" s="20">
+      <c r="AJ11" s="26">
         <f>SUM(AF11*AB11)</f>
       </c>
       <c r="AK11" s="4"/>
       <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
       <c r="AN11" s="5"/>
-      <c r="AO11" s="20"/>
+      <c r="AO11" s="26"/>
       <c r="AP11" s="4"/>
       <c r="AQ11" s="4"/>
       <c r="AR11" s="5"/>
-      <c r="AS11" s="20">
+      <c r="AS11" s="26">
         <f>SUM(AO11*AB11)</f>
       </c>
       <c r="AT11" s="4"/>
       <c r="AU11" s="4"/>
       <c r="AV11" s="4"/>
       <c r="AW11" s="5"/>
-      <c r="AX11" s="20"/>
+      <c r="AX11" s="26"/>
       <c r="AY11" s="4"/>
       <c r="AZ11" s="4"/>
       <c r="BA11" s="4"/>
       <c r="BB11" s="5"/>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="10"/>
@@ -1534,40 +1567,40 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="10"/>
-      <c r="AB12" s="18"/>
+      <c r="AB12" s="24"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="20"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="26"/>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
       <c r="AI12" s="5"/>
-      <c r="AJ12" s="20">
+      <c r="AJ12" s="26">
         <f>SUM(AF12*AB12)</f>
       </c>
       <c r="AK12" s="4"/>
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="20"/>
+      <c r="AO12" s="26"/>
       <c r="AP12" s="4"/>
       <c r="AQ12" s="4"/>
       <c r="AR12" s="5"/>
-      <c r="AS12" s="20">
+      <c r="AS12" s="26">
         <f>SUM(AO12*AB12)</f>
       </c>
       <c r="AT12" s="4"/>
       <c r="AU12" s="4"/>
       <c r="AV12" s="4"/>
       <c r="AW12" s="5"/>
-      <c r="AX12" s="20"/>
+      <c r="AX12" s="26"/>
       <c r="AY12" s="4"/>
       <c r="AZ12" s="4"/>
       <c r="BA12" s="4"/>
       <c r="BB12" s="5"/>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="10"/>
@@ -1594,40 +1627,40 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
       <c r="AA13" s="10"/>
-      <c r="AB13" s="18"/>
+      <c r="AB13" s="24"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="20"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="26"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
       <c r="AI13" s="5"/>
-      <c r="AJ13" s="20">
+      <c r="AJ13" s="26">
         <f>SUM(AF13*AB13)</f>
       </c>
       <c r="AK13" s="4"/>
       <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
       <c r="AN13" s="5"/>
-      <c r="AO13" s="20"/>
+      <c r="AO13" s="26"/>
       <c r="AP13" s="4"/>
       <c r="AQ13" s="4"/>
       <c r="AR13" s="5"/>
-      <c r="AS13" s="20">
+      <c r="AS13" s="26">
         <f>SUM(AO13*AB13)</f>
       </c>
       <c r="AT13" s="4"/>
       <c r="AU13" s="4"/>
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
-      <c r="AX13" s="20"/>
+      <c r="AX13" s="26"/>
       <c r="AY13" s="4"/>
       <c r="AZ13" s="4"/>
       <c r="BA13" s="4"/>
       <c r="BB13" s="5"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -1654,44 +1687,44 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
-      <c r="AB14" s="18"/>
+      <c r="AB14" s="24"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
-      <c r="AE14" s="19"/>
-      <c r="AF14" s="20"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="26"/>
       <c r="AG14" s="4"/>
       <c r="AH14" s="4"/>
       <c r="AI14" s="5"/>
-      <c r="AJ14" s="20">
+      <c r="AJ14" s="26">
         <f>SUM(AF14*AB14)</f>
       </c>
       <c r="AK14" s="4"/>
       <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
       <c r="AN14" s="5"/>
-      <c r="AO14" s="20"/>
+      <c r="AO14" s="26"/>
       <c r="AP14" s="4"/>
       <c r="AQ14" s="4"/>
       <c r="AR14" s="5"/>
-      <c r="AS14" s="20">
+      <c r="AS14" s="26">
         <f>SUM(AO14*AB14)</f>
       </c>
       <c r="AT14" s="4"/>
       <c r="AU14" s="4"/>
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
-      <c r="AX14" s="20"/>
+      <c r="AX14" s="26"/>
       <c r="AY14" s="4"/>
       <c r="AZ14" s="4"/>
       <c r="BA14" s="4"/>
       <c r="BB14" s="5"/>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="26"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
@@ -1714,40 +1747,40 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
       <c r="AA15" s="10"/>
-      <c r="AB15" s="18"/>
+      <c r="AB15" s="24"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
-      <c r="AE15" s="19"/>
-      <c r="AF15" s="20"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="26"/>
       <c r="AG15" s="4"/>
       <c r="AH15" s="4"/>
       <c r="AI15" s="5"/>
-      <c r="AJ15" s="20">
+      <c r="AJ15" s="26">
         <f>SUM(AF15*AB15)</f>
       </c>
       <c r="AK15" s="4"/>
       <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
       <c r="AN15" s="5"/>
-      <c r="AO15" s="20"/>
+      <c r="AO15" s="26"/>
       <c r="AP15" s="4"/>
       <c r="AQ15" s="4"/>
       <c r="AR15" s="5"/>
-      <c r="AS15" s="20">
+      <c r="AS15" s="26">
         <f>SUM(AO15*AB15)</f>
       </c>
       <c r="AT15" s="4"/>
       <c r="AU15" s="4"/>
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
-      <c r="AX15" s="20"/>
+      <c r="AX15" s="26"/>
       <c r="AY15" s="4"/>
       <c r="AZ15" s="4"/>
       <c r="BA15" s="4"/>
       <c r="BB15" s="5"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="10"/>
@@ -1774,40 +1807,40 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
-      <c r="AB16" s="18"/>
+      <c r="AB16" s="24"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
-      <c r="AE16" s="19"/>
-      <c r="AF16" s="20"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="26"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
       <c r="AI16" s="5"/>
-      <c r="AJ16" s="20">
+      <c r="AJ16" s="26">
         <f>SUM(AF16*AB16)</f>
       </c>
       <c r="AK16" s="4"/>
       <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
       <c r="AN16" s="5"/>
-      <c r="AO16" s="20"/>
+      <c r="AO16" s="26"/>
       <c r="AP16" s="4"/>
       <c r="AQ16" s="4"/>
       <c r="AR16" s="5"/>
-      <c r="AS16" s="20">
+      <c r="AS16" s="26">
         <f>SUM(AO16*AB16)</f>
       </c>
       <c r="AT16" s="4"/>
       <c r="AU16" s="4"/>
       <c r="AV16" s="4"/>
       <c r="AW16" s="5"/>
-      <c r="AX16" s="20"/>
+      <c r="AX16" s="26"/>
       <c r="AY16" s="4"/>
       <c r="AZ16" s="4"/>
       <c r="BA16" s="4"/>
       <c r="BB16" s="5"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="10"/>
@@ -1834,40 +1867,40 @@
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
       <c r="AA17" s="10"/>
-      <c r="AB17" s="18"/>
+      <c r="AB17" s="24"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
-      <c r="AE17" s="19"/>
-      <c r="AF17" s="20"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="26"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
       <c r="AI17" s="5"/>
-      <c r="AJ17" s="20">
+      <c r="AJ17" s="26">
         <f>SUM(AF17*AB17)</f>
       </c>
       <c r="AK17" s="4"/>
       <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
       <c r="AN17" s="5"/>
-      <c r="AO17" s="20"/>
+      <c r="AO17" s="26"/>
       <c r="AP17" s="4"/>
       <c r="AQ17" s="4"/>
       <c r="AR17" s="5"/>
-      <c r="AS17" s="20">
+      <c r="AS17" s="26">
         <f>SUM(AO17*AB17)</f>
       </c>
       <c r="AT17" s="4"/>
       <c r="AU17" s="4"/>
       <c r="AV17" s="4"/>
       <c r="AW17" s="5"/>
-      <c r="AX17" s="20"/>
+      <c r="AX17" s="26"/>
       <c r="AY17" s="4"/>
       <c r="AZ17" s="4"/>
       <c r="BA17" s="4"/>
       <c r="BB17" s="5"/>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="10"/>
@@ -1894,40 +1927,40 @@
       <c r="Y18" s="9"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
-      <c r="AB18" s="18"/>
+      <c r="AB18" s="24"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="20"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="26"/>
       <c r="AG18" s="4"/>
       <c r="AH18" s="4"/>
       <c r="AI18" s="5"/>
-      <c r="AJ18" s="20">
+      <c r="AJ18" s="26">
         <f>SUM(AF18*AB18)</f>
       </c>
       <c r="AK18" s="4"/>
       <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
       <c r="AN18" s="5"/>
-      <c r="AO18" s="20"/>
+      <c r="AO18" s="26"/>
       <c r="AP18" s="4"/>
       <c r="AQ18" s="4"/>
       <c r="AR18" s="5"/>
-      <c r="AS18" s="20">
+      <c r="AS18" s="26">
         <f>SUM(AO18*AB18)</f>
       </c>
       <c r="AT18" s="4"/>
       <c r="AU18" s="4"/>
       <c r="AV18" s="4"/>
       <c r="AW18" s="5"/>
-      <c r="AX18" s="20"/>
+      <c r="AX18" s="26"/>
       <c r="AY18" s="4"/>
       <c r="AZ18" s="4"/>
       <c r="BA18" s="4"/>
       <c r="BB18" s="5"/>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="10"/>
@@ -1939,7 +1972,7 @@
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="10"/>
-      <c r="M19" s="25"/>
+      <c r="M19" s="31"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
@@ -1954,40 +1987,40 @@
       <c r="Y19" s="9"/>
       <c r="Z19" s="9"/>
       <c r="AA19" s="10"/>
-      <c r="AB19" s="18"/>
+      <c r="AB19" s="24"/>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
-      <c r="AE19" s="19"/>
-      <c r="AF19" s="20"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="26"/>
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
       <c r="AI19" s="5"/>
-      <c r="AJ19" s="20">
+      <c r="AJ19" s="26">
         <f>SUM(AF19*AB19)</f>
       </c>
       <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
       <c r="AN19" s="5"/>
-      <c r="AO19" s="20"/>
+      <c r="AO19" s="26"/>
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
       <c r="AR19" s="5"/>
-      <c r="AS19" s="20">
+      <c r="AS19" s="26">
         <f>SUM(AO19*AB19)</f>
       </c>
       <c r="AT19" s="4"/>
       <c r="AU19" s="4"/>
       <c r="AV19" s="4"/>
       <c r="AW19" s="5"/>
-      <c r="AX19" s="20"/>
+      <c r="AX19" s="26"/>
       <c r="AY19" s="4"/>
       <c r="AZ19" s="4"/>
       <c r="BA19" s="4"/>
       <c r="BB19" s="5"/>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
+      <c r="A20" s="27"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
@@ -2014,40 +2047,40 @@
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
-      <c r="AB20" s="18"/>
+      <c r="AB20" s="24"/>
       <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="20"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="26"/>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
       <c r="AI20" s="5"/>
-      <c r="AJ20" s="20">
+      <c r="AJ20" s="26">
         <f>SUM(AF20*AB20)</f>
       </c>
       <c r="AK20" s="4"/>
       <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
       <c r="AN20" s="5"/>
-      <c r="AO20" s="20"/>
+      <c r="AO20" s="26"/>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
       <c r="AR20" s="5"/>
-      <c r="AS20" s="20">
+      <c r="AS20" s="26">
         <f>SUM(AO20*AB20)</f>
       </c>
       <c r="AT20" s="4"/>
       <c r="AU20" s="4"/>
       <c r="AV20" s="4"/>
       <c r="AW20" s="5"/>
-      <c r="AX20" s="20"/>
+      <c r="AX20" s="26"/>
       <c r="AY20" s="4"/>
       <c r="AZ20" s="4"/>
       <c r="BA20" s="4"/>
       <c r="BB20" s="5"/>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="10"/>
@@ -2074,40 +2107,40 @@
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
       <c r="AA21" s="10"/>
-      <c r="AB21" s="18"/>
+      <c r="AB21" s="24"/>
       <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
-      <c r="AE21" s="19"/>
-      <c r="AF21" s="20"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="26"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
       <c r="AI21" s="5"/>
-      <c r="AJ21" s="20">
+      <c r="AJ21" s="26">
         <f>SUM(AF21*AB21)</f>
       </c>
       <c r="AK21" s="4"/>
       <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
       <c r="AN21" s="5"/>
-      <c r="AO21" s="20"/>
+      <c r="AO21" s="26"/>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
       <c r="AR21" s="5"/>
-      <c r="AS21" s="20">
+      <c r="AS21" s="26">
         <f>SUM(AO21*AB21)</f>
       </c>
       <c r="AT21" s="4"/>
       <c r="AU21" s="4"/>
       <c r="AV21" s="4"/>
       <c r="AW21" s="5"/>
-      <c r="AX21" s="20"/>
+      <c r="AX21" s="26"/>
       <c r="AY21" s="4"/>
       <c r="AZ21" s="4"/>
       <c r="BA21" s="4"/>
       <c r="BB21" s="5"/>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="10"/>
@@ -2134,40 +2167,40 @@
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
       <c r="AA22" s="10"/>
-      <c r="AB22" s="18"/>
+      <c r="AB22" s="24"/>
       <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
-      <c r="AE22" s="19"/>
-      <c r="AF22" s="20"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="26"/>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
       <c r="AI22" s="5"/>
-      <c r="AJ22" s="20">
+      <c r="AJ22" s="26">
         <f>SUM(AF22*AB22)</f>
       </c>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
       <c r="AN22" s="5"/>
-      <c r="AO22" s="20"/>
+      <c r="AO22" s="26"/>
       <c r="AP22" s="4"/>
       <c r="AQ22" s="4"/>
       <c r="AR22" s="5"/>
-      <c r="AS22" s="20">
+      <c r="AS22" s="26">
         <f>SUM(AO22*AB22)</f>
       </c>
       <c r="AT22" s="4"/>
       <c r="AU22" s="4"/>
       <c r="AV22" s="4"/>
       <c r="AW22" s="5"/>
-      <c r="AX22" s="20"/>
+      <c r="AX22" s="26"/>
       <c r="AY22" s="4"/>
       <c r="AZ22" s="4"/>
       <c r="BA22" s="4"/>
       <c r="BB22" s="5"/>
     </row>
     <row r="23" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="21"/>
+      <c r="A23" s="27"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -2194,40 +2227,40 @@
       <c r="Y23" s="9"/>
       <c r="Z23" s="9"/>
       <c r="AA23" s="10"/>
-      <c r="AB23" s="18"/>
+      <c r="AB23" s="24"/>
       <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="20"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="26"/>
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
       <c r="AI23" s="5"/>
-      <c r="AJ23" s="20">
+      <c r="AJ23" s="26">
         <f>SUM(AF23*AB23)</f>
       </c>
       <c r="AK23" s="4"/>
       <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="5"/>
-      <c r="AO23" s="20"/>
+      <c r="AO23" s="26"/>
       <c r="AP23" s="4"/>
       <c r="AQ23" s="4"/>
       <c r="AR23" s="5"/>
-      <c r="AS23" s="20">
+      <c r="AS23" s="26">
         <f>SUM(AO23*AB23)</f>
       </c>
       <c r="AT23" s="4"/>
       <c r="AU23" s="4"/>
       <c r="AV23" s="4"/>
       <c r="AW23" s="5"/>
-      <c r="AX23" s="20"/>
+      <c r="AX23" s="26"/>
       <c r="AY23" s="4"/>
       <c r="AZ23" s="4"/>
       <c r="BA23" s="4"/>
       <c r="BB23" s="5"/>
     </row>
     <row r="24" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="21"/>
+      <c r="A24" s="27"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="10"/>
@@ -2254,40 +2287,40 @@
       <c r="Y24" s="9"/>
       <c r="Z24" s="9"/>
       <c r="AA24" s="10"/>
-      <c r="AB24" s="18"/>
+      <c r="AB24" s="24"/>
       <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="20"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="26"/>
       <c r="AG24" s="4"/>
       <c r="AH24" s="4"/>
       <c r="AI24" s="5"/>
-      <c r="AJ24" s="20">
+      <c r="AJ24" s="26">
         <f>SUM(AF24*AB24)</f>
       </c>
       <c r="AK24" s="4"/>
       <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
       <c r="AN24" s="5"/>
-      <c r="AO24" s="20"/>
+      <c r="AO24" s="26"/>
       <c r="AP24" s="4"/>
       <c r="AQ24" s="4"/>
       <c r="AR24" s="5"/>
-      <c r="AS24" s="20">
+      <c r="AS24" s="26">
         <f>SUM(AO24*AB24)</f>
       </c>
       <c r="AT24" s="4"/>
       <c r="AU24" s="4"/>
       <c r="AV24" s="4"/>
       <c r="AW24" s="5"/>
-      <c r="AX24" s="20"/>
+      <c r="AX24" s="26"/>
       <c r="AY24" s="4"/>
       <c r="AZ24" s="4"/>
       <c r="BA24" s="4"/>
       <c r="BB24" s="5"/>
     </row>
     <row r="25" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="10"/>
@@ -2314,33 +2347,33 @@
       <c r="Y25" s="9"/>
       <c r="Z25" s="9"/>
       <c r="AA25" s="10"/>
-      <c r="AB25" s="18"/>
+      <c r="AB25" s="24"/>
       <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="20"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="26"/>
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
       <c r="AI25" s="5"/>
-      <c r="AJ25" s="20">
+      <c r="AJ25" s="26">
         <f>SUM(AF25*AB25)</f>
       </c>
       <c r="AK25" s="4"/>
       <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
       <c r="AN25" s="5"/>
-      <c r="AO25" s="20"/>
+      <c r="AO25" s="26"/>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="5"/>
-      <c r="AS25" s="20">
+      <c r="AS25" s="26">
         <f>SUM(AO25*AB25)</f>
       </c>
       <c r="AT25" s="4"/>
       <c r="AU25" s="4"/>
       <c r="AV25" s="4"/>
       <c r="AW25" s="5"/>
-      <c r="AX25" s="20"/>
+      <c r="AX25" s="26"/>
       <c r="AY25" s="4"/>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
@@ -2348,7 +2381,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1" spans="21:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="U26" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -2363,12 +2396,12 @@
       <c r="AD26" s="9"/>
       <c r="AE26" s="10"/>
       <c r="AF26" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
       <c r="AI26" s="10"/>
-      <c r="AJ26" s="27">
+      <c r="AJ26" s="33">
         <f>SUM(AJ3:AJ25)</f>
       </c>
       <c r="AK26" s="9"/>
@@ -2376,19 +2409,19 @@
       <c r="AM26" s="9"/>
       <c r="AN26" s="10"/>
       <c r="AO26" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
       <c r="AR26" s="10"/>
-      <c r="AS26" s="27">
+      <c r="AS26" s="33">
         <f>SUM(AS3:AS25)</f>
       </c>
       <c r="AT26" s="9"/>
       <c r="AU26" s="9"/>
       <c r="AV26" s="9"/>
       <c r="AW26" s="10"/>
-      <c r="AX26" s="27"/>
+      <c r="AX26" s="33"/>
       <c r="AY26" s="9"/>
       <c r="AZ26" s="9"/>
       <c r="BA26" s="9"/>
@@ -2396,75 +2429,75 @@
     </row>
     <row r="28" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H29" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H31" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H32" s="23" t="s">
-        <v>75</v>
+      <c r="H32" s="29" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H33" s="23" t="s">
-        <v>76</v>
+      <c r="H33" s="29" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H34" s="23" t="s">
-        <v>77</v>
+      <c r="H34" s="29" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H35" s="23" t="s">
-        <v>78</v>
+      <c r="H35" s="29" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H36" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H37" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H38" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H39" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H40" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H41" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3326,64 +3359,80 @@
       <c r="BB8" s="5"/>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="15"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
-      <c r="AD9" s="5"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="9"/>
-      <c r="AG9" s="9"/>
-      <c r="AH9" s="9"/>
-      <c r="AI9" s="9"/>
-      <c r="AJ9" s="10"/>
-      <c r="AK9" s="15"/>
-      <c r="AL9" s="4"/>
-      <c r="AM9" s="4"/>
-      <c r="AN9" s="5"/>
-      <c r="AO9" s="13"/>
-      <c r="AP9" s="9"/>
-      <c r="AQ9" s="9"/>
-      <c r="AR9" s="9"/>
-      <c r="AS9" s="9"/>
-      <c r="AT9" s="10"/>
+      <c r="A9" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="15">
+        <f>SUM(G3:L8)</f>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="19">
+        <f>SUM(M3:R8)</f>
+      </c>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="15">
+        <f>SUM(S3:X8)</f>
+      </c>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="18"/>
+      <c r="Y9" s="15">
+        <f>SUM(Y3:AD8)</f>
+      </c>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="18"/>
+      <c r="AE9" s="19">
+        <f>SUM(AE3:AJ8)</f>
+      </c>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="18"/>
+      <c r="AK9" s="15">
+        <f>SUM(AK3:AN8)</f>
+      </c>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="17"/>
+      <c r="AN9" s="18"/>
+      <c r="AO9" s="13">
+        <f>SUM(AO3:AT8)</f>
+      </c>
+      <c r="AP9" s="20"/>
+      <c r="AQ9" s="20"/>
+      <c r="AR9" s="20"/>
+      <c r="AS9" s="20"/>
+      <c r="AT9" s="21"/>
       <c r="AU9" s="14"/>
-      <c r="AV9" s="4"/>
-      <c r="AW9" s="4"/>
-      <c r="AX9" s="4"/>
-      <c r="AY9" s="4"/>
-      <c r="AZ9" s="4"/>
-      <c r="BA9" s="4"/>
-      <c r="BB9" s="5"/>
+      <c r="AV9" s="17"/>
+      <c r="AW9" s="17"/>
+      <c r="AX9" s="17"/>
+      <c r="AY9" s="17"/>
+      <c r="AZ9" s="17"/>
+      <c r="BA9" s="17"/>
+      <c r="BB9" s="18"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>20</v>
+      <c r="A10" s="22" t="s">
+        <v>21</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -3441,13 +3490,13 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="5"/>
       <c r="E11" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -3457,7 +3506,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="5"/>
       <c r="M11" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
@@ -3467,50 +3516,50 @@
       <c r="S11" s="4"/>
       <c r="T11" s="5"/>
       <c r="U11" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V11" s="4"/>
       <c r="W11" s="5"/>
       <c r="X11" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
       <c r="AA11" s="5"/>
       <c r="AB11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="5"/>
       <c r="AF11" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK11" s="4"/>
       <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
       <c r="AN11" s="5"/>
       <c r="AO11" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP11" s="4"/>
       <c r="AQ11" s="4"/>
       <c r="AR11" s="5"/>
       <c r="AS11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AT11" s="4"/>
       <c r="AU11" s="4"/>
       <c r="AV11" s="4"/>
       <c r="AW11" s="5"/>
       <c r="AX11" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AY11" s="4"/>
       <c r="AZ11" s="4"/>
@@ -3518,14 +3567,14 @@
       <c r="BB11" s="5"/>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17">
+      <c r="A12" s="23">
         <v>46045</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="5"/>
       <c r="E12" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -3535,7 +3584,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="5"/>
       <c r="M12" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
@@ -3545,52 +3594,52 @@
       <c r="S12" s="4"/>
       <c r="T12" s="5"/>
       <c r="U12" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V12" s="4"/>
       <c r="W12" s="5"/>
       <c r="X12" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
       <c r="AA12" s="5"/>
-      <c r="AB12" s="18">
+      <c r="AB12" s="24">
         <v>6</v>
       </c>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
-      <c r="AE12" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF12" s="20">
+      <c r="AE12" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF12" s="26">
         <v>77.27</v>
       </c>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
       <c r="AI12" s="5"/>
-      <c r="AJ12" s="20">
+      <c r="AJ12" s="26">
         <f>SUM(AF12*AB12)</f>
       </c>
       <c r="AK12" s="4"/>
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="20">
+      <c r="AO12" s="26">
         <v>120</v>
       </c>
       <c r="AP12" s="4"/>
       <c r="AQ12" s="4"/>
       <c r="AR12" s="5"/>
-      <c r="AS12" s="20">
+      <c r="AS12" s="26">
         <f>SUM(AO12*AB12)</f>
       </c>
       <c r="AT12" s="4"/>
       <c r="AU12" s="4"/>
       <c r="AV12" s="4"/>
       <c r="AW12" s="5"/>
-      <c r="AX12" s="20" t="s">
-        <v>34</v>
+      <c r="AX12" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY12" s="4"/>
       <c r="AZ12" s="4"/>
@@ -3598,14 +3647,14 @@
       <c r="BB12" s="5"/>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17">
+      <c r="A13" s="23">
         <v>46052</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="5"/>
       <c r="E13" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -3615,7 +3664,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="5"/>
       <c r="M13" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
@@ -3625,52 +3674,52 @@
       <c r="S13" s="4"/>
       <c r="T13" s="5"/>
       <c r="U13" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V13" s="4"/>
       <c r="W13" s="5"/>
       <c r="X13" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
       <c r="AA13" s="5"/>
-      <c r="AB13" s="18">
+      <c r="AB13" s="24">
         <v>1</v>
       </c>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
-      <c r="AE13" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF13" s="20" t="s">
-        <v>34</v>
+      <c r="AE13" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF13" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
       <c r="AI13" s="5"/>
-      <c r="AJ13" s="20">
+      <c r="AJ13" s="26">
         <f>SUM(AF13*AB13)</f>
       </c>
       <c r="AK13" s="4"/>
       <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
       <c r="AN13" s="5"/>
-      <c r="AO13" s="20" t="s">
-        <v>34</v>
+      <c r="AO13" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AP13" s="4"/>
       <c r="AQ13" s="4"/>
       <c r="AR13" s="5"/>
-      <c r="AS13" s="20">
+      <c r="AS13" s="26">
         <f>SUM(AO13*AB13)</f>
       </c>
       <c r="AT13" s="4"/>
       <c r="AU13" s="4"/>
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
-      <c r="AX13" s="20" t="s">
-        <v>34</v>
+      <c r="AX13" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY13" s="4"/>
       <c r="AZ13" s="4"/>
@@ -3678,14 +3727,14 @@
       <c r="BB13" s="5"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17">
+      <c r="A14" s="23">
         <v>46052</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="5"/>
       <c r="E14" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -3695,7 +3744,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="5"/>
       <c r="M14" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
@@ -3705,51 +3754,51 @@
       <c r="S14" s="4"/>
       <c r="T14" s="5"/>
       <c r="U14" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V14" s="4"/>
       <c r="W14" s="5"/>
       <c r="X14" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
       <c r="AA14" s="5"/>
-      <c r="AB14" s="18">
+      <c r="AB14" s="24">
         <v>20</v>
       </c>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
-      <c r="AE14" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF14" s="20">
+      <c r="AE14" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF14" s="26">
         <v>150</v>
       </c>
       <c r="AG14" s="4"/>
       <c r="AH14" s="4"/>
       <c r="AI14" s="5"/>
-      <c r="AJ14" s="20">
+      <c r="AJ14" s="26">
         <f>SUM(AF14*AB14)</f>
       </c>
       <c r="AK14" s="4"/>
       <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
       <c r="AN14" s="5"/>
-      <c r="AO14" s="20">
+      <c r="AO14" s="26">
         <v>240</v>
       </c>
       <c r="AP14" s="4"/>
       <c r="AQ14" s="4"/>
       <c r="AR14" s="5"/>
-      <c r="AS14" s="20">
+      <c r="AS14" s="26">
         <f>SUM(AO14*AB14)</f>
       </c>
       <c r="AT14" s="4"/>
       <c r="AU14" s="4"/>
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
-      <c r="AX14" s="20">
+      <c r="AX14" s="26">
         <v>800</v>
       </c>
       <c r="AY14" s="4"/>
@@ -3758,14 +3807,14 @@
       <c r="BB14" s="5"/>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17">
+      <c r="A15" s="23">
         <v>46053</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="5"/>
       <c r="E15" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -3775,7 +3824,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="5"/>
       <c r="M15" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
@@ -3785,52 +3834,52 @@
       <c r="S15" s="4"/>
       <c r="T15" s="5"/>
       <c r="U15" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V15" s="4"/>
       <c r="W15" s="5"/>
       <c r="X15" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
       <c r="AA15" s="5"/>
-      <c r="AB15" s="18">
+      <c r="AB15" s="24">
         <v>10</v>
       </c>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
-      <c r="AE15" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF15" s="20">
+      <c r="AE15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF15" s="26">
         <v>30</v>
       </c>
       <c r="AG15" s="4"/>
       <c r="AH15" s="4"/>
       <c r="AI15" s="5"/>
-      <c r="AJ15" s="20">
+      <c r="AJ15" s="26">
         <f>SUM(AF15*AB15)</f>
       </c>
       <c r="AK15" s="4"/>
       <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
       <c r="AN15" s="5"/>
-      <c r="AO15" s="20">
+      <c r="AO15" s="26">
         <v>50</v>
       </c>
       <c r="AP15" s="4"/>
       <c r="AQ15" s="4"/>
       <c r="AR15" s="5"/>
-      <c r="AS15" s="20">
+      <c r="AS15" s="26">
         <f>SUM(AO15*AB15)</f>
       </c>
       <c r="AT15" s="4"/>
       <c r="AU15" s="4"/>
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
-      <c r="AX15" s="20" t="s">
-        <v>34</v>
+      <c r="AX15" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY15" s="4"/>
       <c r="AZ15" s="4"/>
@@ -3838,14 +3887,14 @@
       <c r="BB15" s="5"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17">
+      <c r="A16" s="23">
         <v>46054</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="5"/>
       <c r="E16" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -3855,7 +3904,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="5"/>
       <c r="M16" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
@@ -3865,52 +3914,52 @@
       <c r="S16" s="4"/>
       <c r="T16" s="5"/>
       <c r="U16" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V16" s="4"/>
       <c r="W16" s="5"/>
       <c r="X16" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
       <c r="AA16" s="5"/>
-      <c r="AB16" s="18">
+      <c r="AB16" s="24">
         <v>2</v>
       </c>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
-      <c r="AE16" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF16" s="20">
+      <c r="AE16" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF16" s="26">
         <v>2500</v>
       </c>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
       <c r="AI16" s="5"/>
-      <c r="AJ16" s="20">
+      <c r="AJ16" s="26">
         <f>SUM(AF16*AB16)</f>
       </c>
       <c r="AK16" s="4"/>
       <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
       <c r="AN16" s="5"/>
-      <c r="AO16" s="20">
+      <c r="AO16" s="26">
         <v>3800</v>
       </c>
       <c r="AP16" s="4"/>
       <c r="AQ16" s="4"/>
       <c r="AR16" s="5"/>
-      <c r="AS16" s="20">
+      <c r="AS16" s="26">
         <f>SUM(AO16*AB16)</f>
       </c>
       <c r="AT16" s="4"/>
       <c r="AU16" s="4"/>
       <c r="AV16" s="4"/>
       <c r="AW16" s="5"/>
-      <c r="AX16" s="20" t="s">
-        <v>34</v>
+      <c r="AX16" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY16" s="4"/>
       <c r="AZ16" s="4"/>
@@ -3918,14 +3967,14 @@
       <c r="BB16" s="5"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+      <c r="A17" s="23">
         <v>46054</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="5"/>
       <c r="E17" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -3935,7 +3984,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="5"/>
       <c r="M17" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
@@ -3945,51 +3994,51 @@
       <c r="S17" s="4"/>
       <c r="T17" s="5"/>
       <c r="U17" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V17" s="4"/>
       <c r="W17" s="5"/>
       <c r="X17" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
       <c r="AA17" s="5"/>
-      <c r="AB17" s="18">
+      <c r="AB17" s="24">
         <v>1</v>
       </c>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
-      <c r="AE17" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF17" s="20">
+      <c r="AE17" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF17" s="26">
         <v>4200</v>
       </c>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
       <c r="AI17" s="5"/>
-      <c r="AJ17" s="20">
+      <c r="AJ17" s="26">
         <f>SUM(AF17*AB17)</f>
       </c>
       <c r="AK17" s="4"/>
       <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
       <c r="AN17" s="5"/>
-      <c r="AO17" s="20">
+      <c r="AO17" s="26">
         <v>6300</v>
       </c>
       <c r="AP17" s="4"/>
       <c r="AQ17" s="4"/>
       <c r="AR17" s="5"/>
-      <c r="AS17" s="20">
+      <c r="AS17" s="26">
         <f>SUM(AO17*AB17)</f>
       </c>
       <c r="AT17" s="4"/>
       <c r="AU17" s="4"/>
       <c r="AV17" s="4"/>
       <c r="AW17" s="5"/>
-      <c r="AX17" s="20">
+      <c r="AX17" s="26">
         <v>500</v>
       </c>
       <c r="AY17" s="4"/>
@@ -3998,14 +4047,14 @@
       <c r="BB17" s="5"/>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
+      <c r="A18" s="23">
         <v>46055</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="5"/>
       <c r="E18" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -4015,7 +4064,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="5"/>
       <c r="M18" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
@@ -4025,52 +4074,52 @@
       <c r="S18" s="4"/>
       <c r="T18" s="5"/>
       <c r="U18" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V18" s="4"/>
       <c r="W18" s="5"/>
       <c r="X18" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
       <c r="AA18" s="5"/>
-      <c r="AB18" s="18">
+      <c r="AB18" s="24">
         <v>3</v>
       </c>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
-      <c r="AE18" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF18" s="20">
+      <c r="AE18" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF18" s="26">
         <v>180</v>
       </c>
       <c r="AG18" s="4"/>
       <c r="AH18" s="4"/>
       <c r="AI18" s="5"/>
-      <c r="AJ18" s="20">
+      <c r="AJ18" s="26">
         <f>SUM(AF18*AB18)</f>
       </c>
       <c r="AK18" s="4"/>
       <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
       <c r="AN18" s="5"/>
-      <c r="AO18" s="20">
+      <c r="AO18" s="26">
         <v>280</v>
       </c>
       <c r="AP18" s="4"/>
       <c r="AQ18" s="4"/>
       <c r="AR18" s="5"/>
-      <c r="AS18" s="20">
+      <c r="AS18" s="26">
         <f>SUM(AO18*AB18)</f>
       </c>
       <c r="AT18" s="4"/>
       <c r="AU18" s="4"/>
       <c r="AV18" s="4"/>
       <c r="AW18" s="5"/>
-      <c r="AX18" s="20" t="s">
-        <v>34</v>
+      <c r="AX18" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY18" s="4"/>
       <c r="AZ18" s="4"/>
@@ -4078,14 +4127,14 @@
       <c r="BB18" s="5"/>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
+      <c r="A19" s="23">
         <v>46055</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="5"/>
       <c r="E19" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -4095,7 +4144,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="5"/>
       <c r="M19" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -4105,52 +4154,52 @@
       <c r="S19" s="4"/>
       <c r="T19" s="5"/>
       <c r="U19" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V19" s="4"/>
       <c r="W19" s="5"/>
       <c r="X19" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
       <c r="AA19" s="5"/>
-      <c r="AB19" s="18">
+      <c r="AB19" s="24">
         <v>5</v>
       </c>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
-      <c r="AE19" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF19" s="20">
+      <c r="AE19" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF19" s="26">
         <v>90</v>
       </c>
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
       <c r="AI19" s="5"/>
-      <c r="AJ19" s="20">
+      <c r="AJ19" s="26">
         <f>SUM(AF19*AB19)</f>
       </c>
       <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
       <c r="AN19" s="5"/>
-      <c r="AO19" s="20">
+      <c r="AO19" s="26">
         <v>150</v>
       </c>
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
       <c r="AR19" s="5"/>
-      <c r="AS19" s="20">
+      <c r="AS19" s="26">
         <f>SUM(AO19*AB19)</f>
       </c>
       <c r="AT19" s="4"/>
       <c r="AU19" s="4"/>
       <c r="AV19" s="4"/>
       <c r="AW19" s="5"/>
-      <c r="AX19" s="20" t="s">
-        <v>34</v>
+      <c r="AX19" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY19" s="4"/>
       <c r="AZ19" s="4"/>
@@ -4158,14 +4207,14 @@
       <c r="BB19" s="5"/>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21">
+      <c r="A20" s="27">
         <v>46056</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
@@ -4175,7 +4224,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="10"/>
       <c r="M20" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
@@ -4185,52 +4234,52 @@
       <c r="S20" s="9"/>
       <c r="T20" s="10"/>
       <c r="U20" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="10"/>
       <c r="X20" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
-      <c r="AB20" s="18">
+      <c r="AB20" s="24">
         <v>4</v>
       </c>
       <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
-      <c r="AE20" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF20" s="20">
+      <c r="AE20" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF20" s="26">
         <v>600</v>
       </c>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
       <c r="AI20" s="5"/>
-      <c r="AJ20" s="20">
+      <c r="AJ20" s="26">
         <f>SUM(AF20*AB20)</f>
       </c>
       <c r="AK20" s="4"/>
       <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
       <c r="AN20" s="5"/>
-      <c r="AO20" s="20">
+      <c r="AO20" s="26">
         <v>950</v>
       </c>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
       <c r="AR20" s="5"/>
-      <c r="AS20" s="20">
+      <c r="AS20" s="26">
         <f>SUM(AO20*AB20)</f>
       </c>
       <c r="AT20" s="4"/>
       <c r="AU20" s="4"/>
       <c r="AV20" s="4"/>
       <c r="AW20" s="5"/>
-      <c r="AX20" s="20" t="s">
-        <v>34</v>
+      <c r="AX20" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY20" s="4"/>
       <c r="AZ20" s="4"/>
@@ -4238,14 +4287,14 @@
       <c r="BB20" s="5"/>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17">
+      <c r="A21" s="23">
         <v>46056</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="5"/>
       <c r="E21" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -4255,7 +4304,7 @@
       <c r="K21" s="4"/>
       <c r="L21" s="5"/>
       <c r="M21" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
@@ -4265,52 +4314,52 @@
       <c r="S21" s="4"/>
       <c r="T21" s="5"/>
       <c r="U21" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V21" s="4"/>
       <c r="W21" s="5"/>
       <c r="X21" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
       <c r="AA21" s="5"/>
-      <c r="AB21" s="18">
+      <c r="AB21" s="24">
         <v>1</v>
       </c>
       <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
-      <c r="AE21" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF21" s="20">
+      <c r="AE21" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF21" s="26">
         <v>800</v>
       </c>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
       <c r="AI21" s="5"/>
-      <c r="AJ21" s="20">
+      <c r="AJ21" s="26">
         <f>SUM(AF21*AB21)</f>
       </c>
       <c r="AK21" s="4"/>
       <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
       <c r="AN21" s="5"/>
-      <c r="AO21" s="20">
+      <c r="AO21" s="26">
         <v>1200</v>
       </c>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
       <c r="AR21" s="5"/>
-      <c r="AS21" s="20">
+      <c r="AS21" s="26">
         <f>SUM(AO21*AB21)</f>
       </c>
       <c r="AT21" s="4"/>
       <c r="AU21" s="4"/>
       <c r="AV21" s="4"/>
       <c r="AW21" s="5"/>
-      <c r="AX21" s="20" t="s">
-        <v>34</v>
+      <c r="AX21" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY21" s="4"/>
       <c r="AZ21" s="4"/>
@@ -4318,14 +4367,14 @@
       <c r="BB21" s="5"/>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17">
+      <c r="A22" s="23">
         <v>46057</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="5"/>
       <c r="E22" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -4335,7 +4384,7 @@
       <c r="K22" s="4"/>
       <c r="L22" s="5"/>
       <c r="M22" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
@@ -4345,52 +4394,52 @@
       <c r="S22" s="4"/>
       <c r="T22" s="5"/>
       <c r="U22" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V22" s="4"/>
       <c r="W22" s="5"/>
       <c r="X22" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
       <c r="AA22" s="5"/>
-      <c r="AB22" s="18">
+      <c r="AB22" s="24">
         <v>20</v>
       </c>
       <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
-      <c r="AE22" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF22" s="20">
+      <c r="AE22" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF22" s="26">
         <v>15</v>
       </c>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
       <c r="AI22" s="5"/>
-      <c r="AJ22" s="20">
+      <c r="AJ22" s="26">
         <f>SUM(AF22*AB22)</f>
       </c>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
       <c r="AN22" s="5"/>
-      <c r="AO22" s="20">
+      <c r="AO22" s="26">
         <v>30</v>
       </c>
       <c r="AP22" s="4"/>
       <c r="AQ22" s="4"/>
       <c r="AR22" s="5"/>
-      <c r="AS22" s="20">
+      <c r="AS22" s="26">
         <f>SUM(AO22*AB22)</f>
       </c>
       <c r="AT22" s="4"/>
       <c r="AU22" s="4"/>
       <c r="AV22" s="4"/>
       <c r="AW22" s="5"/>
-      <c r="AX22" s="20" t="s">
-        <v>34</v>
+      <c r="AX22" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY22" s="4"/>
       <c r="AZ22" s="4"/>
@@ -4398,14 +4447,14 @@
       <c r="BB22" s="5"/>
     </row>
     <row r="23" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17">
+      <c r="A23" s="23">
         <v>46057</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="5"/>
       <c r="E23" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -4415,7 +4464,7 @@
       <c r="K23" s="4"/>
       <c r="L23" s="5"/>
       <c r="M23" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
@@ -4425,52 +4474,52 @@
       <c r="S23" s="4"/>
       <c r="T23" s="5"/>
       <c r="U23" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V23" s="4"/>
       <c r="W23" s="5"/>
       <c r="X23" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
       <c r="AA23" s="5"/>
-      <c r="AB23" s="18">
+      <c r="AB23" s="24">
         <v>20</v>
       </c>
       <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
-      <c r="AE23" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF23" s="20">
+      <c r="AE23" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF23" s="26">
         <v>8</v>
       </c>
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
       <c r="AI23" s="5"/>
-      <c r="AJ23" s="20">
+      <c r="AJ23" s="26">
         <f>SUM(AF23*AB23)</f>
       </c>
       <c r="AK23" s="4"/>
       <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="5"/>
-      <c r="AO23" s="20">
+      <c r="AO23" s="26">
         <v>20</v>
       </c>
       <c r="AP23" s="4"/>
       <c r="AQ23" s="4"/>
       <c r="AR23" s="5"/>
-      <c r="AS23" s="20">
+      <c r="AS23" s="26">
         <f>SUM(AO23*AB23)</f>
       </c>
       <c r="AT23" s="4"/>
       <c r="AU23" s="4"/>
       <c r="AV23" s="4"/>
       <c r="AW23" s="5"/>
-      <c r="AX23" s="20" t="s">
-        <v>34</v>
+      <c r="AX23" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY23" s="4"/>
       <c r="AZ23" s="4"/>
@@ -4478,14 +4527,14 @@
       <c r="BB23" s="5"/>
     </row>
     <row r="24" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17">
+      <c r="A24" s="23">
         <v>46058</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="5"/>
       <c r="E24" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -4495,7 +4544,7 @@
       <c r="K24" s="4"/>
       <c r="L24" s="5"/>
       <c r="M24" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
@@ -4505,52 +4554,52 @@
       <c r="S24" s="4"/>
       <c r="T24" s="5"/>
       <c r="U24" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V24" s="4"/>
       <c r="W24" s="5"/>
       <c r="X24" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
       <c r="AA24" s="5"/>
-      <c r="AB24" s="18">
+      <c r="AB24" s="24">
         <v>50</v>
       </c>
       <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
-      <c r="AE24" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF24" s="20">
+      <c r="AE24" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF24" s="26">
         <v>6</v>
       </c>
       <c r="AG24" s="4"/>
       <c r="AH24" s="4"/>
       <c r="AI24" s="5"/>
-      <c r="AJ24" s="20">
+      <c r="AJ24" s="26">
         <f>SUM(AF24*AB24)</f>
       </c>
       <c r="AK24" s="4"/>
       <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
       <c r="AN24" s="5"/>
-      <c r="AO24" s="20">
+      <c r="AO24" s="26">
         <v>12</v>
       </c>
       <c r="AP24" s="4"/>
       <c r="AQ24" s="4"/>
       <c r="AR24" s="5"/>
-      <c r="AS24" s="20">
+      <c r="AS24" s="26">
         <f>SUM(AO24*AB24)</f>
       </c>
       <c r="AT24" s="4"/>
       <c r="AU24" s="4"/>
       <c r="AV24" s="4"/>
       <c r="AW24" s="5"/>
-      <c r="AX24" s="20" t="s">
-        <v>34</v>
+      <c r="AX24" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY24" s="4"/>
       <c r="AZ24" s="4"/>
@@ -4558,28 +4607,28 @@
       <c r="BB24" s="5"/>
     </row>
     <row r="25" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="22"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
       <c r="U25" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
@@ -4594,12 +4643,12 @@
       <c r="AD25" s="4"/>
       <c r="AE25" s="5"/>
       <c r="AF25" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
       <c r="AI25" s="5"/>
-      <c r="AJ25" s="20">
+      <c r="AJ25" s="26">
         <f>SUM(AJ12:AJ24)</f>
       </c>
       <c r="AK25" s="4"/>
@@ -4607,19 +4656,19 @@
       <c r="AM25" s="4"/>
       <c r="AN25" s="5"/>
       <c r="AO25" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="5"/>
-      <c r="AS25" s="20">
+      <c r="AS25" s="26">
         <f>SUM(AS12:AS24)</f>
       </c>
       <c r="AT25" s="4"/>
       <c r="AU25" s="4"/>
       <c r="AV25" s="4"/>
       <c r="AW25" s="5"/>
-      <c r="AX25" s="20"/>
+      <c r="AX25" s="26"/>
       <c r="AY25" s="4"/>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
@@ -4628,78 +4677,78 @@
     <row r="26" ht="22.5" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="27" ht="22.5" customHeight="1" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H29" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H30" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="H31" s="23" t="s">
-        <v>75</v>
+      <c r="H31" s="29" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="H32" s="23" t="s">
-        <v>76</v>
+      <c r="H32" s="29" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="H33" s="23" t="s">
-        <v>77</v>
+      <c r="H33" s="29" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="H34" s="23" t="s">
-        <v>78</v>
+      <c r="H34" s="29" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H35" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H36" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H37" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H38" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H39" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1" spans="8:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H40" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -5058,8 +5107,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>20</v>
+      <c r="A1" s="30" t="s">
+        <v>21</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -5117,13 +5166,13 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -5133,7 +5182,7 @@
       <c r="K2" s="9"/>
       <c r="L2" s="10"/>
       <c r="M2" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
@@ -5143,50 +5192,50 @@
       <c r="S2" s="9"/>
       <c r="T2" s="10"/>
       <c r="U2" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V2" s="9"/>
       <c r="W2" s="10"/>
       <c r="X2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="10"/>
       <c r="AB2" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC2" s="9"/>
       <c r="AD2" s="9"/>
       <c r="AE2" s="10"/>
       <c r="AF2" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG2" s="9"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="10"/>
       <c r="AJ2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK2" s="9"/>
       <c r="AL2" s="9"/>
       <c r="AM2" s="9"/>
       <c r="AN2" s="10"/>
       <c r="AO2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP2" s="9"/>
       <c r="AQ2" s="9"/>
       <c r="AR2" s="10"/>
       <c r="AS2" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AT2" s="9"/>
       <c r="AU2" s="9"/>
       <c r="AV2" s="9"/>
       <c r="AW2" s="10"/>
       <c r="AX2" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AY2" s="9"/>
       <c r="AZ2" s="9"/>
@@ -5194,14 +5243,14 @@
       <c r="BB2" s="10"/>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="23">
         <v>46058</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="5"/>
       <c r="E3" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -5211,7 +5260,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="5"/>
       <c r="M3" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -5221,52 +5270,52 @@
       <c r="S3" s="4"/>
       <c r="T3" s="5"/>
       <c r="U3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V3" s="4"/>
       <c r="W3" s="5"/>
       <c r="X3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="5"/>
-      <c r="AB3" s="18">
+      <c r="AB3" s="24">
         <v>2</v>
       </c>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
-      <c r="AE3" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF3" s="20">
+      <c r="AE3" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF3" s="26">
         <v>200</v>
       </c>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
       <c r="AI3" s="5"/>
-      <c r="AJ3" s="20">
+      <c r="AJ3" s="26">
         <f>SUM(AF3*AB3)</f>
       </c>
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
       <c r="AM3" s="4"/>
       <c r="AN3" s="5"/>
-      <c r="AO3" s="20">
+      <c r="AO3" s="26">
         <v>320</v>
       </c>
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="5"/>
-      <c r="AS3" s="20">
+      <c r="AS3" s="26">
         <f>SUM(AO3*AB3)</f>
       </c>
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
       <c r="AV3" s="4"/>
       <c r="AW3" s="5"/>
-      <c r="AX3" s="20" t="s">
-        <v>34</v>
+      <c r="AX3" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="AY3" s="4"/>
       <c r="AZ3" s="4"/>
@@ -5274,14 +5323,14 @@
       <c r="BB3" s="5"/>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21">
+      <c r="A4" s="27">
         <v>46058</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
       <c r="E4" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -5291,7 +5340,7 @@
       <c r="K4" s="9"/>
       <c r="L4" s="10"/>
       <c r="M4" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
@@ -5301,51 +5350,51 @@
       <c r="S4" s="9"/>
       <c r="T4" s="10"/>
       <c r="U4" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V4" s="9"/>
       <c r="W4" s="10"/>
       <c r="X4" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
       <c r="AA4" s="10"/>
-      <c r="AB4" s="18">
+      <c r="AB4" s="24">
         <v>3</v>
       </c>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
-      <c r="AE4" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF4" s="20">
+      <c r="AE4" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF4" s="26">
         <v>450</v>
       </c>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
       <c r="AI4" s="5"/>
-      <c r="AJ4" s="20">
+      <c r="AJ4" s="26">
         <f>SUM(AF4*AB4)</f>
       </c>
       <c r="AK4" s="4"/>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
       <c r="AN4" s="5"/>
-      <c r="AO4" s="20">
+      <c r="AO4" s="26">
         <v>700</v>
       </c>
       <c r="AP4" s="4"/>
       <c r="AQ4" s="4"/>
       <c r="AR4" s="5"/>
-      <c r="AS4" s="20">
+      <c r="AS4" s="26">
         <f>SUM(AO4*AB4)</f>
       </c>
       <c r="AT4" s="4"/>
       <c r="AU4" s="4"/>
       <c r="AV4" s="4"/>
       <c r="AW4" s="5"/>
-      <c r="AX4" s="20">
+      <c r="AX4" s="26">
         <v>600</v>
       </c>
       <c r="AY4" s="4"/>
@@ -5354,11 +5403,11 @@
       <c r="BB4" s="5"/>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="10"/>
-      <c r="E5" s="25"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -5381,40 +5430,40 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
       <c r="AA5" s="10"/>
-      <c r="AB5" s="18"/>
+      <c r="AB5" s="24"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
-      <c r="AE5" s="19"/>
-      <c r="AF5" s="20"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="26"/>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
       <c r="AI5" s="5"/>
-      <c r="AJ5" s="20">
+      <c r="AJ5" s="26">
         <f>SUM(AF5*AB5)</f>
       </c>
       <c r="AK5" s="4"/>
       <c r="AL5" s="4"/>
       <c r="AM5" s="4"/>
       <c r="AN5" s="5"/>
-      <c r="AO5" s="20"/>
+      <c r="AO5" s="26"/>
       <c r="AP5" s="4"/>
       <c r="AQ5" s="4"/>
       <c r="AR5" s="5"/>
-      <c r="AS5" s="20">
+      <c r="AS5" s="26">
         <f>SUM(AO5*AB5)</f>
       </c>
       <c r="AT5" s="4"/>
       <c r="AU5" s="4"/>
       <c r="AV5" s="4"/>
       <c r="AW5" s="5"/>
-      <c r="AX5" s="20"/>
+      <c r="AX5" s="26"/>
       <c r="AY5" s="4"/>
       <c r="AZ5" s="4"/>
       <c r="BA5" s="4"/>
       <c r="BB5" s="5"/>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="10"/>
@@ -5441,44 +5490,44 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="10"/>
-      <c r="AB6" s="18"/>
+      <c r="AB6" s="24"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="20"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="26"/>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
       <c r="AI6" s="5"/>
-      <c r="AJ6" s="20">
+      <c r="AJ6" s="26">
         <f>SUM(AF6*AB6)</f>
       </c>
       <c r="AK6" s="4"/>
       <c r="AL6" s="4"/>
       <c r="AM6" s="4"/>
       <c r="AN6" s="5"/>
-      <c r="AO6" s="20"/>
+      <c r="AO6" s="26"/>
       <c r="AP6" s="4"/>
       <c r="AQ6" s="4"/>
       <c r="AR6" s="5"/>
-      <c r="AS6" s="20">
+      <c r="AS6" s="26">
         <f>SUM(AO6*AB6)</f>
       </c>
       <c r="AT6" s="4"/>
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
       <c r="AW6" s="5"/>
-      <c r="AX6" s="20"/>
+      <c r="AX6" s="26"/>
       <c r="AY6" s="4"/>
       <c r="AZ6" s="4"/>
       <c r="BA6" s="4"/>
       <c r="BB6" s="5"/>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="26"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -5501,40 +5550,40 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
       <c r="AA7" s="10"/>
-      <c r="AB7" s="18"/>
+      <c r="AB7" s="24"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="20"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="26"/>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="20">
+      <c r="AJ7" s="26">
         <f>SUM(AF7*AB7)</f>
       </c>
       <c r="AK7" s="4"/>
       <c r="AL7" s="4"/>
       <c r="AM7" s="4"/>
       <c r="AN7" s="5"/>
-      <c r="AO7" s="20"/>
+      <c r="AO7" s="26"/>
       <c r="AP7" s="4"/>
       <c r="AQ7" s="4"/>
       <c r="AR7" s="5"/>
-      <c r="AS7" s="20">
+      <c r="AS7" s="26">
         <f>SUM(AO7*AB7)</f>
       </c>
       <c r="AT7" s="4"/>
       <c r="AU7" s="4"/>
       <c r="AV7" s="4"/>
       <c r="AW7" s="5"/>
-      <c r="AX7" s="20"/>
+      <c r="AX7" s="26"/>
       <c r="AY7" s="4"/>
       <c r="AZ7" s="4"/>
       <c r="BA7" s="4"/>
       <c r="BB7" s="5"/>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="10"/>
@@ -5546,7 +5595,7 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="25"/>
+      <c r="M8" s="31"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
@@ -5561,44 +5610,44 @@
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="10"/>
-      <c r="AB8" s="18"/>
+      <c r="AB8" s="24"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="20"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="26"/>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
       <c r="AI8" s="5"/>
-      <c r="AJ8" s="20">
+      <c r="AJ8" s="26">
         <f>SUM(AF8*AB8)</f>
       </c>
       <c r="AK8" s="4"/>
       <c r="AL8" s="4"/>
       <c r="AM8" s="4"/>
       <c r="AN8" s="5"/>
-      <c r="AO8" s="20"/>
+      <c r="AO8" s="26"/>
       <c r="AP8" s="4"/>
       <c r="AQ8" s="4"/>
       <c r="AR8" s="5"/>
-      <c r="AS8" s="20">
+      <c r="AS8" s="26">
         <f>SUM(AO8*AB8)</f>
       </c>
       <c r="AT8" s="4"/>
       <c r="AU8" s="4"/>
       <c r="AV8" s="4"/>
       <c r="AW8" s="5"/>
-      <c r="AX8" s="20"/>
+      <c r="AX8" s="26"/>
       <c r="AY8" s="4"/>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
       <c r="BB8" s="5"/>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="26"/>
+      <c r="E9" s="32"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
@@ -5621,40 +5670,40 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
       <c r="AA9" s="10"/>
-      <c r="AB9" s="18"/>
+      <c r="AB9" s="24"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="20"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="26"/>
       <c r="AG9" s="4"/>
       <c r="AH9" s="4"/>
       <c r="AI9" s="5"/>
-      <c r="AJ9" s="20">
+      <c r="AJ9" s="26">
         <f>SUM(AF9*AB9)</f>
       </c>
       <c r="AK9" s="4"/>
       <c r="AL9" s="4"/>
       <c r="AM9" s="4"/>
       <c r="AN9" s="5"/>
-      <c r="AO9" s="20"/>
+      <c r="AO9" s="26"/>
       <c r="AP9" s="4"/>
       <c r="AQ9" s="4"/>
       <c r="AR9" s="5"/>
-      <c r="AS9" s="20">
+      <c r="AS9" s="26">
         <f>SUM(AO9*AB9)</f>
       </c>
       <c r="AT9" s="4"/>
       <c r="AU9" s="4"/>
       <c r="AV9" s="4"/>
       <c r="AW9" s="5"/>
-      <c r="AX9" s="20"/>
+      <c r="AX9" s="26"/>
       <c r="AY9" s="4"/>
       <c r="AZ9" s="4"/>
       <c r="BA9" s="4"/>
       <c r="BB9" s="5"/>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -5681,40 +5730,40 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="10"/>
-      <c r="AB10" s="18"/>
+      <c r="AB10" s="24"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="20"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="26"/>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
       <c r="AI10" s="5"/>
-      <c r="AJ10" s="20">
+      <c r="AJ10" s="26">
         <f>SUM(AF10*AB10)</f>
       </c>
       <c r="AK10" s="4"/>
       <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
       <c r="AN10" s="5"/>
-      <c r="AO10" s="20"/>
+      <c r="AO10" s="26"/>
       <c r="AP10" s="4"/>
       <c r="AQ10" s="4"/>
       <c r="AR10" s="5"/>
-      <c r="AS10" s="20">
+      <c r="AS10" s="26">
         <f>SUM(AO10*AB10)</f>
       </c>
       <c r="AT10" s="4"/>
       <c r="AU10" s="4"/>
       <c r="AV10" s="4"/>
       <c r="AW10" s="5"/>
-      <c r="AX10" s="20"/>
+      <c r="AX10" s="26"/>
       <c r="AY10" s="4"/>
       <c r="AZ10" s="4"/>
       <c r="BA10" s="4"/>
       <c r="BB10" s="5"/>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="10"/>
@@ -5741,40 +5790,40 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
       <c r="AA11" s="10"/>
-      <c r="AB11" s="18"/>
+      <c r="AB11" s="24"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="20"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="26"/>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="5"/>
-      <c r="AJ11" s="20">
+      <c r="AJ11" s="26">
         <f>SUM(AF11*AB11)</f>
       </c>
       <c r="AK11" s="4"/>
       <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
       <c r="AN11" s="5"/>
-      <c r="AO11" s="20"/>
+      <c r="AO11" s="26"/>
       <c r="AP11" s="4"/>
       <c r="AQ11" s="4"/>
       <c r="AR11" s="5"/>
-      <c r="AS11" s="20">
+      <c r="AS11" s="26">
         <f>SUM(AO11*AB11)</f>
       </c>
       <c r="AT11" s="4"/>
       <c r="AU11" s="4"/>
       <c r="AV11" s="4"/>
       <c r="AW11" s="5"/>
-      <c r="AX11" s="20"/>
+      <c r="AX11" s="26"/>
       <c r="AY11" s="4"/>
       <c r="AZ11" s="4"/>
       <c r="BA11" s="4"/>
       <c r="BB11" s="5"/>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="10"/>
@@ -5801,40 +5850,40 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="10"/>
-      <c r="AB12" s="18"/>
+      <c r="AB12" s="24"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="20"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="26"/>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
       <c r="AI12" s="5"/>
-      <c r="AJ12" s="20">
+      <c r="AJ12" s="26">
         <f>SUM(AF12*AB12)</f>
       </c>
       <c r="AK12" s="4"/>
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="20"/>
+      <c r="AO12" s="26"/>
       <c r="AP12" s="4"/>
       <c r="AQ12" s="4"/>
       <c r="AR12" s="5"/>
-      <c r="AS12" s="20">
+      <c r="AS12" s="26">
         <f>SUM(AO12*AB12)</f>
       </c>
       <c r="AT12" s="4"/>
       <c r="AU12" s="4"/>
       <c r="AV12" s="4"/>
       <c r="AW12" s="5"/>
-      <c r="AX12" s="20"/>
+      <c r="AX12" s="26"/>
       <c r="AY12" s="4"/>
       <c r="AZ12" s="4"/>
       <c r="BA12" s="4"/>
       <c r="BB12" s="5"/>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="10"/>
@@ -5861,40 +5910,40 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
       <c r="AA13" s="10"/>
-      <c r="AB13" s="18"/>
+      <c r="AB13" s="24"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="20"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="26"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
       <c r="AI13" s="5"/>
-      <c r="AJ13" s="20">
+      <c r="AJ13" s="26">
         <f>SUM(AF13*AB13)</f>
       </c>
       <c r="AK13" s="4"/>
       <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
       <c r="AN13" s="5"/>
-      <c r="AO13" s="20"/>
+      <c r="AO13" s="26"/>
       <c r="AP13" s="4"/>
       <c r="AQ13" s="4"/>
       <c r="AR13" s="5"/>
-      <c r="AS13" s="20">
+      <c r="AS13" s="26">
         <f>SUM(AO13*AB13)</f>
       </c>
       <c r="AT13" s="4"/>
       <c r="AU13" s="4"/>
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
-      <c r="AX13" s="20"/>
+      <c r="AX13" s="26"/>
       <c r="AY13" s="4"/>
       <c r="AZ13" s="4"/>
       <c r="BA13" s="4"/>
       <c r="BB13" s="5"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -5921,44 +5970,44 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
-      <c r="AB14" s="18"/>
+      <c r="AB14" s="24"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
-      <c r="AE14" s="19"/>
-      <c r="AF14" s="20"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="26"/>
       <c r="AG14" s="4"/>
       <c r="AH14" s="4"/>
       <c r="AI14" s="5"/>
-      <c r="AJ14" s="20">
+      <c r="AJ14" s="26">
         <f>SUM(AF14*AB14)</f>
       </c>
       <c r="AK14" s="4"/>
       <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
       <c r="AN14" s="5"/>
-      <c r="AO14" s="20"/>
+      <c r="AO14" s="26"/>
       <c r="AP14" s="4"/>
       <c r="AQ14" s="4"/>
       <c r="AR14" s="5"/>
-      <c r="AS14" s="20">
+      <c r="AS14" s="26">
         <f>SUM(AO14*AB14)</f>
       </c>
       <c r="AT14" s="4"/>
       <c r="AU14" s="4"/>
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
-      <c r="AX14" s="20"/>
+      <c r="AX14" s="26"/>
       <c r="AY14" s="4"/>
       <c r="AZ14" s="4"/>
       <c r="BA14" s="4"/>
       <c r="BB14" s="5"/>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="26"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
@@ -5981,40 +6030,40 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
       <c r="AA15" s="10"/>
-      <c r="AB15" s="18"/>
+      <c r="AB15" s="24"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
-      <c r="AE15" s="19"/>
-      <c r="AF15" s="20"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="26"/>
       <c r="AG15" s="4"/>
       <c r="AH15" s="4"/>
       <c r="AI15" s="5"/>
-      <c r="AJ15" s="20">
+      <c r="AJ15" s="26">
         <f>SUM(AF15*AB15)</f>
       </c>
       <c r="AK15" s="4"/>
       <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
       <c r="AN15" s="5"/>
-      <c r="AO15" s="20"/>
+      <c r="AO15" s="26"/>
       <c r="AP15" s="4"/>
       <c r="AQ15" s="4"/>
       <c r="AR15" s="5"/>
-      <c r="AS15" s="20">
+      <c r="AS15" s="26">
         <f>SUM(AO15*AB15)</f>
       </c>
       <c r="AT15" s="4"/>
       <c r="AU15" s="4"/>
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
-      <c r="AX15" s="20"/>
+      <c r="AX15" s="26"/>
       <c r="AY15" s="4"/>
       <c r="AZ15" s="4"/>
       <c r="BA15" s="4"/>
       <c r="BB15" s="5"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="10"/>
@@ -6041,40 +6090,40 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
-      <c r="AB16" s="18"/>
+      <c r="AB16" s="24"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
-      <c r="AE16" s="19"/>
-      <c r="AF16" s="20"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="26"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
       <c r="AI16" s="5"/>
-      <c r="AJ16" s="20">
+      <c r="AJ16" s="26">
         <f>SUM(AF16*AB16)</f>
       </c>
       <c r="AK16" s="4"/>
       <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
       <c r="AN16" s="5"/>
-      <c r="AO16" s="20"/>
+      <c r="AO16" s="26"/>
       <c r="AP16" s="4"/>
       <c r="AQ16" s="4"/>
       <c r="AR16" s="5"/>
-      <c r="AS16" s="20">
+      <c r="AS16" s="26">
         <f>SUM(AO16*AB16)</f>
       </c>
       <c r="AT16" s="4"/>
       <c r="AU16" s="4"/>
       <c r="AV16" s="4"/>
       <c r="AW16" s="5"/>
-      <c r="AX16" s="20"/>
+      <c r="AX16" s="26"/>
       <c r="AY16" s="4"/>
       <c r="AZ16" s="4"/>
       <c r="BA16" s="4"/>
       <c r="BB16" s="5"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="10"/>
@@ -6101,40 +6150,40 @@
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
       <c r="AA17" s="10"/>
-      <c r="AB17" s="18"/>
+      <c r="AB17" s="24"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
-      <c r="AE17" s="19"/>
-      <c r="AF17" s="20"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="26"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
       <c r="AI17" s="5"/>
-      <c r="AJ17" s="20">
+      <c r="AJ17" s="26">
         <f>SUM(AF17*AB17)</f>
       </c>
       <c r="AK17" s="4"/>
       <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
       <c r="AN17" s="5"/>
-      <c r="AO17" s="20"/>
+      <c r="AO17" s="26"/>
       <c r="AP17" s="4"/>
       <c r="AQ17" s="4"/>
       <c r="AR17" s="5"/>
-      <c r="AS17" s="20">
+      <c r="AS17" s="26">
         <f>SUM(AO17*AB17)</f>
       </c>
       <c r="AT17" s="4"/>
       <c r="AU17" s="4"/>
       <c r="AV17" s="4"/>
       <c r="AW17" s="5"/>
-      <c r="AX17" s="20"/>
+      <c r="AX17" s="26"/>
       <c r="AY17" s="4"/>
       <c r="AZ17" s="4"/>
       <c r="BA17" s="4"/>
       <c r="BB17" s="5"/>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="10"/>
@@ -6161,40 +6210,40 @@
       <c r="Y18" s="9"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
-      <c r="AB18" s="18"/>
+      <c r="AB18" s="24"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="20"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="26"/>
       <c r="AG18" s="4"/>
       <c r="AH18" s="4"/>
       <c r="AI18" s="5"/>
-      <c r="AJ18" s="20">
+      <c r="AJ18" s="26">
         <f>SUM(AF18*AB18)</f>
       </c>
       <c r="AK18" s="4"/>
       <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
       <c r="AN18" s="5"/>
-      <c r="AO18" s="20"/>
+      <c r="AO18" s="26"/>
       <c r="AP18" s="4"/>
       <c r="AQ18" s="4"/>
       <c r="AR18" s="5"/>
-      <c r="AS18" s="20">
+      <c r="AS18" s="26">
         <f>SUM(AO18*AB18)</f>
       </c>
       <c r="AT18" s="4"/>
       <c r="AU18" s="4"/>
       <c r="AV18" s="4"/>
       <c r="AW18" s="5"/>
-      <c r="AX18" s="20"/>
+      <c r="AX18" s="26"/>
       <c r="AY18" s="4"/>
       <c r="AZ18" s="4"/>
       <c r="BA18" s="4"/>
       <c r="BB18" s="5"/>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="10"/>
@@ -6206,7 +6255,7 @@
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="10"/>
-      <c r="M19" s="25"/>
+      <c r="M19" s="31"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
@@ -6221,40 +6270,40 @@
       <c r="Y19" s="9"/>
       <c r="Z19" s="9"/>
       <c r="AA19" s="10"/>
-      <c r="AB19" s="18"/>
+      <c r="AB19" s="24"/>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
-      <c r="AE19" s="19"/>
-      <c r="AF19" s="20"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="26"/>
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
       <c r="AI19" s="5"/>
-      <c r="AJ19" s="20">
+      <c r="AJ19" s="26">
         <f>SUM(AF19*AB19)</f>
       </c>
       <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
       <c r="AN19" s="5"/>
-      <c r="AO19" s="20"/>
+      <c r="AO19" s="26"/>
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
       <c r="AR19" s="5"/>
-      <c r="AS19" s="20">
+      <c r="AS19" s="26">
         <f>SUM(AO19*AB19)</f>
       </c>
       <c r="AT19" s="4"/>
       <c r="AU19" s="4"/>
       <c r="AV19" s="4"/>
       <c r="AW19" s="5"/>
-      <c r="AX19" s="20"/>
+      <c r="AX19" s="26"/>
       <c r="AY19" s="4"/>
       <c r="AZ19" s="4"/>
       <c r="BA19" s="4"/>
       <c r="BB19" s="5"/>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
+      <c r="A20" s="27"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
@@ -6281,40 +6330,40 @@
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
-      <c r="AB20" s="18"/>
+      <c r="AB20" s="24"/>
       <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="20"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="26"/>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
       <c r="AI20" s="5"/>
-      <c r="AJ20" s="20">
+      <c r="AJ20" s="26">
         <f>SUM(AF20*AB20)</f>
       </c>
       <c r="AK20" s="4"/>
       <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
       <c r="AN20" s="5"/>
-      <c r="AO20" s="20"/>
+      <c r="AO20" s="26"/>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
       <c r="AR20" s="5"/>
-      <c r="AS20" s="20">
+      <c r="AS20" s="26">
         <f>SUM(AO20*AB20)</f>
       </c>
       <c r="AT20" s="4"/>
       <c r="AU20" s="4"/>
       <c r="AV20" s="4"/>
       <c r="AW20" s="5"/>
-      <c r="AX20" s="20"/>
+      <c r="AX20" s="26"/>
       <c r="AY20" s="4"/>
       <c r="AZ20" s="4"/>
       <c r="BA20" s="4"/>
       <c r="BB20" s="5"/>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="10"/>
@@ -6341,40 +6390,40 @@
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
       <c r="AA21" s="10"/>
-      <c r="AB21" s="18"/>
+      <c r="AB21" s="24"/>
       <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
-      <c r="AE21" s="19"/>
-      <c r="AF21" s="20"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="26"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
       <c r="AI21" s="5"/>
-      <c r="AJ21" s="20">
+      <c r="AJ21" s="26">
         <f>SUM(AF21*AB21)</f>
       </c>
       <c r="AK21" s="4"/>
       <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
       <c r="AN21" s="5"/>
-      <c r="AO21" s="20"/>
+      <c r="AO21" s="26"/>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
       <c r="AR21" s="5"/>
-      <c r="AS21" s="20">
+      <c r="AS21" s="26">
         <f>SUM(AO21*AB21)</f>
       </c>
       <c r="AT21" s="4"/>
       <c r="AU21" s="4"/>
       <c r="AV21" s="4"/>
       <c r="AW21" s="5"/>
-      <c r="AX21" s="20"/>
+      <c r="AX21" s="26"/>
       <c r="AY21" s="4"/>
       <c r="AZ21" s="4"/>
       <c r="BA21" s="4"/>
       <c r="BB21" s="5"/>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="10"/>
@@ -6401,40 +6450,40 @@
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
       <c r="AA22" s="10"/>
-      <c r="AB22" s="18"/>
+      <c r="AB22" s="24"/>
       <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
-      <c r="AE22" s="19"/>
-      <c r="AF22" s="20"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="26"/>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
       <c r="AI22" s="5"/>
-      <c r="AJ22" s="20">
+      <c r="AJ22" s="26">
         <f>SUM(AF22*AB22)</f>
       </c>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
       <c r="AN22" s="5"/>
-      <c r="AO22" s="20"/>
+      <c r="AO22" s="26"/>
       <c r="AP22" s="4"/>
       <c r="AQ22" s="4"/>
       <c r="AR22" s="5"/>
-      <c r="AS22" s="20">
+      <c r="AS22" s="26">
         <f>SUM(AO22*AB22)</f>
       </c>
       <c r="AT22" s="4"/>
       <c r="AU22" s="4"/>
       <c r="AV22" s="4"/>
       <c r="AW22" s="5"/>
-      <c r="AX22" s="20"/>
+      <c r="AX22" s="26"/>
       <c r="AY22" s="4"/>
       <c r="AZ22" s="4"/>
       <c r="BA22" s="4"/>
       <c r="BB22" s="5"/>
     </row>
     <row r="23" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="21"/>
+      <c r="A23" s="27"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -6461,40 +6510,40 @@
       <c r="Y23" s="9"/>
       <c r="Z23" s="9"/>
       <c r="AA23" s="10"/>
-      <c r="AB23" s="18"/>
+      <c r="AB23" s="24"/>
       <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="20"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="26"/>
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
       <c r="AI23" s="5"/>
-      <c r="AJ23" s="20">
+      <c r="AJ23" s="26">
         <f>SUM(AF23*AB23)</f>
       </c>
       <c r="AK23" s="4"/>
       <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="5"/>
-      <c r="AO23" s="20"/>
+      <c r="AO23" s="26"/>
       <c r="AP23" s="4"/>
       <c r="AQ23" s="4"/>
       <c r="AR23" s="5"/>
-      <c r="AS23" s="20">
+      <c r="AS23" s="26">
         <f>SUM(AO23*AB23)</f>
       </c>
       <c r="AT23" s="4"/>
       <c r="AU23" s="4"/>
       <c r="AV23" s="4"/>
       <c r="AW23" s="5"/>
-      <c r="AX23" s="20"/>
+      <c r="AX23" s="26"/>
       <c r="AY23" s="4"/>
       <c r="AZ23" s="4"/>
       <c r="BA23" s="4"/>
       <c r="BB23" s="5"/>
     </row>
     <row r="24" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="21"/>
+      <c r="A24" s="27"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="10"/>
@@ -6521,40 +6570,40 @@
       <c r="Y24" s="9"/>
       <c r="Z24" s="9"/>
       <c r="AA24" s="10"/>
-      <c r="AB24" s="18"/>
+      <c r="AB24" s="24"/>
       <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="20"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="26"/>
       <c r="AG24" s="4"/>
       <c r="AH24" s="4"/>
       <c r="AI24" s="5"/>
-      <c r="AJ24" s="20">
+      <c r="AJ24" s="26">
         <f>SUM(AF24*AB24)</f>
       </c>
       <c r="AK24" s="4"/>
       <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
       <c r="AN24" s="5"/>
-      <c r="AO24" s="20"/>
+      <c r="AO24" s="26"/>
       <c r="AP24" s="4"/>
       <c r="AQ24" s="4"/>
       <c r="AR24" s="5"/>
-      <c r="AS24" s="20">
+      <c r="AS24" s="26">
         <f>SUM(AO24*AB24)</f>
       </c>
       <c r="AT24" s="4"/>
       <c r="AU24" s="4"/>
       <c r="AV24" s="4"/>
       <c r="AW24" s="5"/>
-      <c r="AX24" s="20"/>
+      <c r="AX24" s="26"/>
       <c r="AY24" s="4"/>
       <c r="AZ24" s="4"/>
       <c r="BA24" s="4"/>
       <c r="BB24" s="5"/>
     </row>
     <row r="25" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="10"/>
@@ -6581,33 +6630,33 @@
       <c r="Y25" s="9"/>
       <c r="Z25" s="9"/>
       <c r="AA25" s="10"/>
-      <c r="AB25" s="18"/>
+      <c r="AB25" s="24"/>
       <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="20"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="26"/>
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
       <c r="AI25" s="5"/>
-      <c r="AJ25" s="20">
+      <c r="AJ25" s="26">
         <f>SUM(AF25*AB25)</f>
       </c>
       <c r="AK25" s="4"/>
       <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
       <c r="AN25" s="5"/>
-      <c r="AO25" s="20"/>
+      <c r="AO25" s="26"/>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="5"/>
-      <c r="AS25" s="20">
+      <c r="AS25" s="26">
         <f>SUM(AO25*AB25)</f>
       </c>
       <c r="AT25" s="4"/>
       <c r="AU25" s="4"/>
       <c r="AV25" s="4"/>
       <c r="AW25" s="5"/>
-      <c r="AX25" s="20"/>
+      <c r="AX25" s="26"/>
       <c r="AY25" s="4"/>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
@@ -6615,7 +6664,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1" spans="21:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="U26" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -6630,12 +6679,12 @@
       <c r="AD26" s="9"/>
       <c r="AE26" s="10"/>
       <c r="AF26" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
       <c r="AI26" s="10"/>
-      <c r="AJ26" s="27">
+      <c r="AJ26" s="33">
         <f>SUM(AJ3:AJ25)</f>
       </c>
       <c r="AK26" s="9"/>
@@ -6643,19 +6692,19 @@
       <c r="AM26" s="9"/>
       <c r="AN26" s="10"/>
       <c r="AO26" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
       <c r="AR26" s="10"/>
-      <c r="AS26" s="27">
+      <c r="AS26" s="33">
         <f>SUM(AS3:AS25)</f>
       </c>
       <c r="AT26" s="9"/>
       <c r="AU26" s="9"/>
       <c r="AV26" s="9"/>
       <c r="AW26" s="10"/>
-      <c r="AX26" s="27"/>
+      <c r="AX26" s="33"/>
       <c r="AY26" s="9"/>
       <c r="AZ26" s="9"/>
       <c r="BA26" s="9"/>
@@ -6663,78 +6712,78 @@
     </row>
     <row r="28" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H31" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H32" s="23" t="s">
-        <v>75</v>
+      <c r="H32" s="29" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H33" s="23" t="s">
-        <v>76</v>
+      <c r="H33" s="29" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H34" s="23" t="s">
-        <v>77</v>
+      <c r="H34" s="29" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H35" s="23" t="s">
-        <v>78</v>
+      <c r="H35" s="29" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H36" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H37" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H38" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H39" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H40" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H41" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -7059,8 +7108,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>20</v>
+      <c r="A1" s="30" t="s">
+        <v>21</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -7118,13 +7167,13 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -7134,7 +7183,7 @@
       <c r="K2" s="9"/>
       <c r="L2" s="10"/>
       <c r="M2" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
@@ -7144,50 +7193,50 @@
       <c r="S2" s="9"/>
       <c r="T2" s="10"/>
       <c r="U2" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V2" s="9"/>
       <c r="W2" s="10"/>
       <c r="X2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="10"/>
       <c r="AB2" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC2" s="9"/>
       <c r="AD2" s="9"/>
       <c r="AE2" s="10"/>
       <c r="AF2" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG2" s="9"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="10"/>
       <c r="AJ2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK2" s="9"/>
       <c r="AL2" s="9"/>
       <c r="AM2" s="9"/>
       <c r="AN2" s="10"/>
       <c r="AO2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP2" s="9"/>
       <c r="AQ2" s="9"/>
       <c r="AR2" s="10"/>
       <c r="AS2" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AT2" s="9"/>
       <c r="AU2" s="9"/>
       <c r="AV2" s="9"/>
       <c r="AW2" s="10"/>
       <c r="AX2" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AY2" s="9"/>
       <c r="AZ2" s="9"/>
@@ -7195,7 +7244,7 @@
       <c r="BB2" s="10"/>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21"/>
+      <c r="A3" s="27"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
@@ -7222,44 +7271,44 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
       <c r="AA3" s="10"/>
-      <c r="AB3" s="18"/>
+      <c r="AB3" s="24"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
-      <c r="AE3" s="19"/>
-      <c r="AF3" s="20"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="26"/>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
       <c r="AI3" s="5"/>
-      <c r="AJ3" s="20">
+      <c r="AJ3" s="26">
         <f>SUM(AF3*AB3)</f>
       </c>
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
       <c r="AM3" s="4"/>
       <c r="AN3" s="5"/>
-      <c r="AO3" s="20"/>
+      <c r="AO3" s="26"/>
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="5"/>
-      <c r="AS3" s="20">
+      <c r="AS3" s="26">
         <f>SUM(AO3*AB3)</f>
       </c>
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
       <c r="AV3" s="4"/>
       <c r="AW3" s="5"/>
-      <c r="AX3" s="20"/>
+      <c r="AX3" s="26"/>
       <c r="AY3" s="4"/>
       <c r="AZ3" s="4"/>
       <c r="BA3" s="4"/>
       <c r="BB3" s="5"/>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="25"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -7282,44 +7331,44 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
       <c r="AA4" s="10"/>
-      <c r="AB4" s="18"/>
+      <c r="AB4" s="24"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
-      <c r="AE4" s="19"/>
-      <c r="AF4" s="20"/>
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="26"/>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
       <c r="AI4" s="5"/>
-      <c r="AJ4" s="20">
+      <c r="AJ4" s="26">
         <f>SUM(AF4*AB4)</f>
       </c>
       <c r="AK4" s="4"/>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
       <c r="AN4" s="5"/>
-      <c r="AO4" s="20"/>
+      <c r="AO4" s="26"/>
       <c r="AP4" s="4"/>
       <c r="AQ4" s="4"/>
       <c r="AR4" s="5"/>
-      <c r="AS4" s="20">
+      <c r="AS4" s="26">
         <f>SUM(AO4*AB4)</f>
       </c>
       <c r="AT4" s="4"/>
       <c r="AU4" s="4"/>
       <c r="AV4" s="4"/>
       <c r="AW4" s="5"/>
-      <c r="AX4" s="20"/>
+      <c r="AX4" s="26"/>
       <c r="AY4" s="4"/>
       <c r="AZ4" s="4"/>
       <c r="BA4" s="4"/>
       <c r="BB4" s="5"/>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="10"/>
-      <c r="E5" s="25"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -7342,40 +7391,40 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
       <c r="AA5" s="10"/>
-      <c r="AB5" s="18"/>
+      <c r="AB5" s="24"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
-      <c r="AE5" s="19"/>
-      <c r="AF5" s="20"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="26"/>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
       <c r="AI5" s="5"/>
-      <c r="AJ5" s="20">
+      <c r="AJ5" s="26">
         <f>SUM(AF5*AB5)</f>
       </c>
       <c r="AK5" s="4"/>
       <c r="AL5" s="4"/>
       <c r="AM5" s="4"/>
       <c r="AN5" s="5"/>
-      <c r="AO5" s="20"/>
+      <c r="AO5" s="26"/>
       <c r="AP5" s="4"/>
       <c r="AQ5" s="4"/>
       <c r="AR5" s="5"/>
-      <c r="AS5" s="20">
+      <c r="AS5" s="26">
         <f>SUM(AO5*AB5)</f>
       </c>
       <c r="AT5" s="4"/>
       <c r="AU5" s="4"/>
       <c r="AV5" s="4"/>
       <c r="AW5" s="5"/>
-      <c r="AX5" s="20"/>
+      <c r="AX5" s="26"/>
       <c r="AY5" s="4"/>
       <c r="AZ5" s="4"/>
       <c r="BA5" s="4"/>
       <c r="BB5" s="5"/>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="10"/>
@@ -7402,44 +7451,44 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="10"/>
-      <c r="AB6" s="18"/>
+      <c r="AB6" s="24"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="20"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="26"/>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
       <c r="AI6" s="5"/>
-      <c r="AJ6" s="20">
+      <c r="AJ6" s="26">
         <f>SUM(AF6*AB6)</f>
       </c>
       <c r="AK6" s="4"/>
       <c r="AL6" s="4"/>
       <c r="AM6" s="4"/>
       <c r="AN6" s="5"/>
-      <c r="AO6" s="20"/>
+      <c r="AO6" s="26"/>
       <c r="AP6" s="4"/>
       <c r="AQ6" s="4"/>
       <c r="AR6" s="5"/>
-      <c r="AS6" s="20">
+      <c r="AS6" s="26">
         <f>SUM(AO6*AB6)</f>
       </c>
       <c r="AT6" s="4"/>
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
       <c r="AW6" s="5"/>
-      <c r="AX6" s="20"/>
+      <c r="AX6" s="26"/>
       <c r="AY6" s="4"/>
       <c r="AZ6" s="4"/>
       <c r="BA6" s="4"/>
       <c r="BB6" s="5"/>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="26"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -7462,40 +7511,40 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
       <c r="AA7" s="10"/>
-      <c r="AB7" s="18"/>
+      <c r="AB7" s="24"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="20"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="26"/>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="20">
+      <c r="AJ7" s="26">
         <f>SUM(AF7*AB7)</f>
       </c>
       <c r="AK7" s="4"/>
       <c r="AL7" s="4"/>
       <c r="AM7" s="4"/>
       <c r="AN7" s="5"/>
-      <c r="AO7" s="20"/>
+      <c r="AO7" s="26"/>
       <c r="AP7" s="4"/>
       <c r="AQ7" s="4"/>
       <c r="AR7" s="5"/>
-      <c r="AS7" s="20">
+      <c r="AS7" s="26">
         <f>SUM(AO7*AB7)</f>
       </c>
       <c r="AT7" s="4"/>
       <c r="AU7" s="4"/>
       <c r="AV7" s="4"/>
       <c r="AW7" s="5"/>
-      <c r="AX7" s="20"/>
+      <c r="AX7" s="26"/>
       <c r="AY7" s="4"/>
       <c r="AZ7" s="4"/>
       <c r="BA7" s="4"/>
       <c r="BB7" s="5"/>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="10"/>
@@ -7507,7 +7556,7 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="25"/>
+      <c r="M8" s="31"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
@@ -7522,44 +7571,44 @@
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="10"/>
-      <c r="AB8" s="18"/>
+      <c r="AB8" s="24"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="20"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="26"/>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
       <c r="AI8" s="5"/>
-      <c r="AJ8" s="20">
+      <c r="AJ8" s="26">
         <f>SUM(AF8*AB8)</f>
       </c>
       <c r="AK8" s="4"/>
       <c r="AL8" s="4"/>
       <c r="AM8" s="4"/>
       <c r="AN8" s="5"/>
-      <c r="AO8" s="20"/>
+      <c r="AO8" s="26"/>
       <c r="AP8" s="4"/>
       <c r="AQ8" s="4"/>
       <c r="AR8" s="5"/>
-      <c r="AS8" s="20">
+      <c r="AS8" s="26">
         <f>SUM(AO8*AB8)</f>
       </c>
       <c r="AT8" s="4"/>
       <c r="AU8" s="4"/>
       <c r="AV8" s="4"/>
       <c r="AW8" s="5"/>
-      <c r="AX8" s="20"/>
+      <c r="AX8" s="26"/>
       <c r="AY8" s="4"/>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
       <c r="BB8" s="5"/>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="26"/>
+      <c r="E9" s="32"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
@@ -7582,40 +7631,40 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
       <c r="AA9" s="10"/>
-      <c r="AB9" s="18"/>
+      <c r="AB9" s="24"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="20"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="26"/>
       <c r="AG9" s="4"/>
       <c r="AH9" s="4"/>
       <c r="AI9" s="5"/>
-      <c r="AJ9" s="20">
+      <c r="AJ9" s="26">
         <f>SUM(AF9*AB9)</f>
       </c>
       <c r="AK9" s="4"/>
       <c r="AL9" s="4"/>
       <c r="AM9" s="4"/>
       <c r="AN9" s="5"/>
-      <c r="AO9" s="20"/>
+      <c r="AO9" s="26"/>
       <c r="AP9" s="4"/>
       <c r="AQ9" s="4"/>
       <c r="AR9" s="5"/>
-      <c r="AS9" s="20">
+      <c r="AS9" s="26">
         <f>SUM(AO9*AB9)</f>
       </c>
       <c r="AT9" s="4"/>
       <c r="AU9" s="4"/>
       <c r="AV9" s="4"/>
       <c r="AW9" s="5"/>
-      <c r="AX9" s="20"/>
+      <c r="AX9" s="26"/>
       <c r="AY9" s="4"/>
       <c r="AZ9" s="4"/>
       <c r="BA9" s="4"/>
       <c r="BB9" s="5"/>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7642,40 +7691,40 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="10"/>
-      <c r="AB10" s="18"/>
+      <c r="AB10" s="24"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="20"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="26"/>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
       <c r="AI10" s="5"/>
-      <c r="AJ10" s="20">
+      <c r="AJ10" s="26">
         <f>SUM(AF10*AB10)</f>
       </c>
       <c r="AK10" s="4"/>
       <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
       <c r="AN10" s="5"/>
-      <c r="AO10" s="20"/>
+      <c r="AO10" s="26"/>
       <c r="AP10" s="4"/>
       <c r="AQ10" s="4"/>
       <c r="AR10" s="5"/>
-      <c r="AS10" s="20">
+      <c r="AS10" s="26">
         <f>SUM(AO10*AB10)</f>
       </c>
       <c r="AT10" s="4"/>
       <c r="AU10" s="4"/>
       <c r="AV10" s="4"/>
       <c r="AW10" s="5"/>
-      <c r="AX10" s="20"/>
+      <c r="AX10" s="26"/>
       <c r="AY10" s="4"/>
       <c r="AZ10" s="4"/>
       <c r="BA10" s="4"/>
       <c r="BB10" s="5"/>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="10"/>
@@ -7702,40 +7751,40 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
       <c r="AA11" s="10"/>
-      <c r="AB11" s="18"/>
+      <c r="AB11" s="24"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="20"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="26"/>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="5"/>
-      <c r="AJ11" s="20">
+      <c r="AJ11" s="26">
         <f>SUM(AF11*AB11)</f>
       </c>
       <c r="AK11" s="4"/>
       <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
       <c r="AN11" s="5"/>
-      <c r="AO11" s="20"/>
+      <c r="AO11" s="26"/>
       <c r="AP11" s="4"/>
       <c r="AQ11" s="4"/>
       <c r="AR11" s="5"/>
-      <c r="AS11" s="20">
+      <c r="AS11" s="26">
         <f>SUM(AO11*AB11)</f>
       </c>
       <c r="AT11" s="4"/>
       <c r="AU11" s="4"/>
       <c r="AV11" s="4"/>
       <c r="AW11" s="5"/>
-      <c r="AX11" s="20"/>
+      <c r="AX11" s="26"/>
       <c r="AY11" s="4"/>
       <c r="AZ11" s="4"/>
       <c r="BA11" s="4"/>
       <c r="BB11" s="5"/>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="10"/>
@@ -7762,40 +7811,40 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="10"/>
-      <c r="AB12" s="18"/>
+      <c r="AB12" s="24"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="20"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="26"/>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
       <c r="AI12" s="5"/>
-      <c r="AJ12" s="20">
+      <c r="AJ12" s="26">
         <f>SUM(AF12*AB12)</f>
       </c>
       <c r="AK12" s="4"/>
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="20"/>
+      <c r="AO12" s="26"/>
       <c r="AP12" s="4"/>
       <c r="AQ12" s="4"/>
       <c r="AR12" s="5"/>
-      <c r="AS12" s="20">
+      <c r="AS12" s="26">
         <f>SUM(AO12*AB12)</f>
       </c>
       <c r="AT12" s="4"/>
       <c r="AU12" s="4"/>
       <c r="AV12" s="4"/>
       <c r="AW12" s="5"/>
-      <c r="AX12" s="20"/>
+      <c r="AX12" s="26"/>
       <c r="AY12" s="4"/>
       <c r="AZ12" s="4"/>
       <c r="BA12" s="4"/>
       <c r="BB12" s="5"/>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="10"/>
@@ -7822,40 +7871,40 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
       <c r="AA13" s="10"/>
-      <c r="AB13" s="18"/>
+      <c r="AB13" s="24"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="20"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="26"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
       <c r="AI13" s="5"/>
-      <c r="AJ13" s="20">
+      <c r="AJ13" s="26">
         <f>SUM(AF13*AB13)</f>
       </c>
       <c r="AK13" s="4"/>
       <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
       <c r="AN13" s="5"/>
-      <c r="AO13" s="20"/>
+      <c r="AO13" s="26"/>
       <c r="AP13" s="4"/>
       <c r="AQ13" s="4"/>
       <c r="AR13" s="5"/>
-      <c r="AS13" s="20">
+      <c r="AS13" s="26">
         <f>SUM(AO13*AB13)</f>
       </c>
       <c r="AT13" s="4"/>
       <c r="AU13" s="4"/>
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
-      <c r="AX13" s="20"/>
+      <c r="AX13" s="26"/>
       <c r="AY13" s="4"/>
       <c r="AZ13" s="4"/>
       <c r="BA13" s="4"/>
       <c r="BB13" s="5"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7882,44 +7931,44 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
-      <c r="AB14" s="18"/>
+      <c r="AB14" s="24"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
-      <c r="AE14" s="19"/>
-      <c r="AF14" s="20"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="26"/>
       <c r="AG14" s="4"/>
       <c r="AH14" s="4"/>
       <c r="AI14" s="5"/>
-      <c r="AJ14" s="20">
+      <c r="AJ14" s="26">
         <f>SUM(AF14*AB14)</f>
       </c>
       <c r="AK14" s="4"/>
       <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
       <c r="AN14" s="5"/>
-      <c r="AO14" s="20"/>
+      <c r="AO14" s="26"/>
       <c r="AP14" s="4"/>
       <c r="AQ14" s="4"/>
       <c r="AR14" s="5"/>
-      <c r="AS14" s="20">
+      <c r="AS14" s="26">
         <f>SUM(AO14*AB14)</f>
       </c>
       <c r="AT14" s="4"/>
       <c r="AU14" s="4"/>
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
-      <c r="AX14" s="20"/>
+      <c r="AX14" s="26"/>
       <c r="AY14" s="4"/>
       <c r="AZ14" s="4"/>
       <c r="BA14" s="4"/>
       <c r="BB14" s="5"/>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="26"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
@@ -7942,40 +7991,40 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
       <c r="AA15" s="10"/>
-      <c r="AB15" s="18"/>
+      <c r="AB15" s="24"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
-      <c r="AE15" s="19"/>
-      <c r="AF15" s="20"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="26"/>
       <c r="AG15" s="4"/>
       <c r="AH15" s="4"/>
       <c r="AI15" s="5"/>
-      <c r="AJ15" s="20">
+      <c r="AJ15" s="26">
         <f>SUM(AF15*AB15)</f>
       </c>
       <c r="AK15" s="4"/>
       <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
       <c r="AN15" s="5"/>
-      <c r="AO15" s="20"/>
+      <c r="AO15" s="26"/>
       <c r="AP15" s="4"/>
       <c r="AQ15" s="4"/>
       <c r="AR15" s="5"/>
-      <c r="AS15" s="20">
+      <c r="AS15" s="26">
         <f>SUM(AO15*AB15)</f>
       </c>
       <c r="AT15" s="4"/>
       <c r="AU15" s="4"/>
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
-      <c r="AX15" s="20"/>
+      <c r="AX15" s="26"/>
       <c r="AY15" s="4"/>
       <c r="AZ15" s="4"/>
       <c r="BA15" s="4"/>
       <c r="BB15" s="5"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="10"/>
@@ -8002,40 +8051,40 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
-      <c r="AB16" s="18"/>
+      <c r="AB16" s="24"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
-      <c r="AE16" s="19"/>
-      <c r="AF16" s="20"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="26"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
       <c r="AI16" s="5"/>
-      <c r="AJ16" s="20">
+      <c r="AJ16" s="26">
         <f>SUM(AF16*AB16)</f>
       </c>
       <c r="AK16" s="4"/>
       <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
       <c r="AN16" s="5"/>
-      <c r="AO16" s="20"/>
+      <c r="AO16" s="26"/>
       <c r="AP16" s="4"/>
       <c r="AQ16" s="4"/>
       <c r="AR16" s="5"/>
-      <c r="AS16" s="20">
+      <c r="AS16" s="26">
         <f>SUM(AO16*AB16)</f>
       </c>
       <c r="AT16" s="4"/>
       <c r="AU16" s="4"/>
       <c r="AV16" s="4"/>
       <c r="AW16" s="5"/>
-      <c r="AX16" s="20"/>
+      <c r="AX16" s="26"/>
       <c r="AY16" s="4"/>
       <c r="AZ16" s="4"/>
       <c r="BA16" s="4"/>
       <c r="BB16" s="5"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="10"/>
@@ -8062,40 +8111,40 @@
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
       <c r="AA17" s="10"/>
-      <c r="AB17" s="18"/>
+      <c r="AB17" s="24"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
-      <c r="AE17" s="19"/>
-      <c r="AF17" s="20"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="26"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
       <c r="AI17" s="5"/>
-      <c r="AJ17" s="20">
+      <c r="AJ17" s="26">
         <f>SUM(AF17*AB17)</f>
       </c>
       <c r="AK17" s="4"/>
       <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
       <c r="AN17" s="5"/>
-      <c r="AO17" s="20"/>
+      <c r="AO17" s="26"/>
       <c r="AP17" s="4"/>
       <c r="AQ17" s="4"/>
       <c r="AR17" s="5"/>
-      <c r="AS17" s="20">
+      <c r="AS17" s="26">
         <f>SUM(AO17*AB17)</f>
       </c>
       <c r="AT17" s="4"/>
       <c r="AU17" s="4"/>
       <c r="AV17" s="4"/>
       <c r="AW17" s="5"/>
-      <c r="AX17" s="20"/>
+      <c r="AX17" s="26"/>
       <c r="AY17" s="4"/>
       <c r="AZ17" s="4"/>
       <c r="BA17" s="4"/>
       <c r="BB17" s="5"/>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="10"/>
@@ -8122,40 +8171,40 @@
       <c r="Y18" s="9"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
-      <c r="AB18" s="18"/>
+      <c r="AB18" s="24"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="20"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="26"/>
       <c r="AG18" s="4"/>
       <c r="AH18" s="4"/>
       <c r="AI18" s="5"/>
-      <c r="AJ18" s="20">
+      <c r="AJ18" s="26">
         <f>SUM(AF18*AB18)</f>
       </c>
       <c r="AK18" s="4"/>
       <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
       <c r="AN18" s="5"/>
-      <c r="AO18" s="20"/>
+      <c r="AO18" s="26"/>
       <c r="AP18" s="4"/>
       <c r="AQ18" s="4"/>
       <c r="AR18" s="5"/>
-      <c r="AS18" s="20">
+      <c r="AS18" s="26">
         <f>SUM(AO18*AB18)</f>
       </c>
       <c r="AT18" s="4"/>
       <c r="AU18" s="4"/>
       <c r="AV18" s="4"/>
       <c r="AW18" s="5"/>
-      <c r="AX18" s="20"/>
+      <c r="AX18" s="26"/>
       <c r="AY18" s="4"/>
       <c r="AZ18" s="4"/>
       <c r="BA18" s="4"/>
       <c r="BB18" s="5"/>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="10"/>
@@ -8167,7 +8216,7 @@
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="10"/>
-      <c r="M19" s="25"/>
+      <c r="M19" s="31"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
@@ -8182,40 +8231,40 @@
       <c r="Y19" s="9"/>
       <c r="Z19" s="9"/>
       <c r="AA19" s="10"/>
-      <c r="AB19" s="18"/>
+      <c r="AB19" s="24"/>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
-      <c r="AE19" s="19"/>
-      <c r="AF19" s="20"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="26"/>
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
       <c r="AI19" s="5"/>
-      <c r="AJ19" s="20">
+      <c r="AJ19" s="26">
         <f>SUM(AF19*AB19)</f>
       </c>
       <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
       <c r="AN19" s="5"/>
-      <c r="AO19" s="20"/>
+      <c r="AO19" s="26"/>
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
       <c r="AR19" s="5"/>
-      <c r="AS19" s="20">
+      <c r="AS19" s="26">
         <f>SUM(AO19*AB19)</f>
       </c>
       <c r="AT19" s="4"/>
       <c r="AU19" s="4"/>
       <c r="AV19" s="4"/>
       <c r="AW19" s="5"/>
-      <c r="AX19" s="20"/>
+      <c r="AX19" s="26"/>
       <c r="AY19" s="4"/>
       <c r="AZ19" s="4"/>
       <c r="BA19" s="4"/>
       <c r="BB19" s="5"/>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
+      <c r="A20" s="27"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
@@ -8242,40 +8291,40 @@
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
-      <c r="AB20" s="18"/>
+      <c r="AB20" s="24"/>
       <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="20"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="26"/>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
       <c r="AI20" s="5"/>
-      <c r="AJ20" s="20">
+      <c r="AJ20" s="26">
         <f>SUM(AF20*AB20)</f>
       </c>
       <c r="AK20" s="4"/>
       <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
       <c r="AN20" s="5"/>
-      <c r="AO20" s="20"/>
+      <c r="AO20" s="26"/>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
       <c r="AR20" s="5"/>
-      <c r="AS20" s="20">
+      <c r="AS20" s="26">
         <f>SUM(AO20*AB20)</f>
       </c>
       <c r="AT20" s="4"/>
       <c r="AU20" s="4"/>
       <c r="AV20" s="4"/>
       <c r="AW20" s="5"/>
-      <c r="AX20" s="20"/>
+      <c r="AX20" s="26"/>
       <c r="AY20" s="4"/>
       <c r="AZ20" s="4"/>
       <c r="BA20" s="4"/>
       <c r="BB20" s="5"/>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="10"/>
@@ -8302,40 +8351,40 @@
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
       <c r="AA21" s="10"/>
-      <c r="AB21" s="18"/>
+      <c r="AB21" s="24"/>
       <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
-      <c r="AE21" s="19"/>
-      <c r="AF21" s="20"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="26"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
       <c r="AI21" s="5"/>
-      <c r="AJ21" s="20">
+      <c r="AJ21" s="26">
         <f>SUM(AF21*AB21)</f>
       </c>
       <c r="AK21" s="4"/>
       <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
       <c r="AN21" s="5"/>
-      <c r="AO21" s="20"/>
+      <c r="AO21" s="26"/>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
       <c r="AR21" s="5"/>
-      <c r="AS21" s="20">
+      <c r="AS21" s="26">
         <f>SUM(AO21*AB21)</f>
       </c>
       <c r="AT21" s="4"/>
       <c r="AU21" s="4"/>
       <c r="AV21" s="4"/>
       <c r="AW21" s="5"/>
-      <c r="AX21" s="20"/>
+      <c r="AX21" s="26"/>
       <c r="AY21" s="4"/>
       <c r="AZ21" s="4"/>
       <c r="BA21" s="4"/>
       <c r="BB21" s="5"/>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="10"/>
@@ -8362,40 +8411,40 @@
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
       <c r="AA22" s="10"/>
-      <c r="AB22" s="18"/>
+      <c r="AB22" s="24"/>
       <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
-      <c r="AE22" s="19"/>
-      <c r="AF22" s="20"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="26"/>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
       <c r="AI22" s="5"/>
-      <c r="AJ22" s="20">
+      <c r="AJ22" s="26">
         <f>SUM(AF22*AB22)</f>
       </c>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
       <c r="AN22" s="5"/>
-      <c r="AO22" s="20"/>
+      <c r="AO22" s="26"/>
       <c r="AP22" s="4"/>
       <c r="AQ22" s="4"/>
       <c r="AR22" s="5"/>
-      <c r="AS22" s="20">
+      <c r="AS22" s="26">
         <f>SUM(AO22*AB22)</f>
       </c>
       <c r="AT22" s="4"/>
       <c r="AU22" s="4"/>
       <c r="AV22" s="4"/>
       <c r="AW22" s="5"/>
-      <c r="AX22" s="20"/>
+      <c r="AX22" s="26"/>
       <c r="AY22" s="4"/>
       <c r="AZ22" s="4"/>
       <c r="BA22" s="4"/>
       <c r="BB22" s="5"/>
     </row>
     <row r="23" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="21"/>
+      <c r="A23" s="27"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -8422,40 +8471,40 @@
       <c r="Y23" s="9"/>
       <c r="Z23" s="9"/>
       <c r="AA23" s="10"/>
-      <c r="AB23" s="18"/>
+      <c r="AB23" s="24"/>
       <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="20"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="26"/>
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
       <c r="AI23" s="5"/>
-      <c r="AJ23" s="20">
+      <c r="AJ23" s="26">
         <f>SUM(AF23*AB23)</f>
       </c>
       <c r="AK23" s="4"/>
       <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="5"/>
-      <c r="AO23" s="20"/>
+      <c r="AO23" s="26"/>
       <c r="AP23" s="4"/>
       <c r="AQ23" s="4"/>
       <c r="AR23" s="5"/>
-      <c r="AS23" s="20">
+      <c r="AS23" s="26">
         <f>SUM(AO23*AB23)</f>
       </c>
       <c r="AT23" s="4"/>
       <c r="AU23" s="4"/>
       <c r="AV23" s="4"/>
       <c r="AW23" s="5"/>
-      <c r="AX23" s="20"/>
+      <c r="AX23" s="26"/>
       <c r="AY23" s="4"/>
       <c r="AZ23" s="4"/>
       <c r="BA23" s="4"/>
       <c r="BB23" s="5"/>
     </row>
     <row r="24" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="21"/>
+      <c r="A24" s="27"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="10"/>
@@ -8482,40 +8531,40 @@
       <c r="Y24" s="9"/>
       <c r="Z24" s="9"/>
       <c r="AA24" s="10"/>
-      <c r="AB24" s="18"/>
+      <c r="AB24" s="24"/>
       <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="20"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="26"/>
       <c r="AG24" s="4"/>
       <c r="AH24" s="4"/>
       <c r="AI24" s="5"/>
-      <c r="AJ24" s="20">
+      <c r="AJ24" s="26">
         <f>SUM(AF24*AB24)</f>
       </c>
       <c r="AK24" s="4"/>
       <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
       <c r="AN24" s="5"/>
-      <c r="AO24" s="20"/>
+      <c r="AO24" s="26"/>
       <c r="AP24" s="4"/>
       <c r="AQ24" s="4"/>
       <c r="AR24" s="5"/>
-      <c r="AS24" s="20">
+      <c r="AS24" s="26">
         <f>SUM(AO24*AB24)</f>
       </c>
       <c r="AT24" s="4"/>
       <c r="AU24" s="4"/>
       <c r="AV24" s="4"/>
       <c r="AW24" s="5"/>
-      <c r="AX24" s="20"/>
+      <c r="AX24" s="26"/>
       <c r="AY24" s="4"/>
       <c r="AZ24" s="4"/>
       <c r="BA24" s="4"/>
       <c r="BB24" s="5"/>
     </row>
     <row r="25" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="10"/>
@@ -8542,33 +8591,33 @@
       <c r="Y25" s="9"/>
       <c r="Z25" s="9"/>
       <c r="AA25" s="10"/>
-      <c r="AB25" s="18"/>
+      <c r="AB25" s="24"/>
       <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="20"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="26"/>
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
       <c r="AI25" s="5"/>
-      <c r="AJ25" s="20">
+      <c r="AJ25" s="26">
         <f>SUM(AF25*AB25)</f>
       </c>
       <c r="AK25" s="4"/>
       <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
       <c r="AN25" s="5"/>
-      <c r="AO25" s="20"/>
+      <c r="AO25" s="26"/>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="5"/>
-      <c r="AS25" s="20">
+      <c r="AS25" s="26">
         <f>SUM(AO25*AB25)</f>
       </c>
       <c r="AT25" s="4"/>
       <c r="AU25" s="4"/>
       <c r="AV25" s="4"/>
       <c r="AW25" s="5"/>
-      <c r="AX25" s="20"/>
+      <c r="AX25" s="26"/>
       <c r="AY25" s="4"/>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
@@ -8576,7 +8625,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1" spans="21:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="U26" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -8591,12 +8640,12 @@
       <c r="AD26" s="9"/>
       <c r="AE26" s="10"/>
       <c r="AF26" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
       <c r="AI26" s="10"/>
-      <c r="AJ26" s="27">
+      <c r="AJ26" s="33">
         <f>SUM(AJ3:AJ25)</f>
       </c>
       <c r="AK26" s="9"/>
@@ -8604,19 +8653,19 @@
       <c r="AM26" s="9"/>
       <c r="AN26" s="10"/>
       <c r="AO26" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
       <c r="AR26" s="10"/>
-      <c r="AS26" s="27">
+      <c r="AS26" s="33">
         <f>SUM(AS3:AS25)</f>
       </c>
       <c r="AT26" s="9"/>
       <c r="AU26" s="9"/>
       <c r="AV26" s="9"/>
       <c r="AW26" s="10"/>
-      <c r="AX26" s="27"/>
+      <c r="AX26" s="33"/>
       <c r="AY26" s="9"/>
       <c r="AZ26" s="9"/>
       <c r="BA26" s="9"/>
@@ -8624,75 +8673,75 @@
     </row>
     <row r="28" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H29" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H31" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H32" s="23" t="s">
-        <v>75</v>
+      <c r="H32" s="29" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H33" s="23" t="s">
-        <v>76</v>
+      <c r="H33" s="29" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H34" s="23" t="s">
-        <v>77</v>
+      <c r="H34" s="29" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H35" s="23" t="s">
-        <v>78</v>
+      <c r="H35" s="29" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H36" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H37" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H38" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H39" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H40" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H41" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/docs/verify/sample_materials.xlsx
+++ b/docs/verify/sample_materials.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">'材料持出表 (3)'!$A1:$BB26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'材料持出表 (4)'!$A1:$BB26</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
